--- a/RevGame_Client/配置表/战斗数值参数.xlsx
+++ b/RevGame_Client/配置表/战斗数值参数.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -604,11 +604,11 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>敌人每隔几个行动周期最多靠近一次（整数 ≥1）；默认 4 个周期 = 5 秒。攻击不受此限。</t>
+          <t>敌人每隔几个行动周期最多移动一次（整数≥1）；默认2个周期=2.5秒，不改变攻击频率。</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>18</v>
+        <v>4.5</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="B64" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
@@ -1539,6 +1539,111 @@
       <c r="C71" s="4" t="inlineStr">
         <is>
           <t>判定“人数落后”：我方棋数 × 本值 &lt; 敌方棋数时，奖励获得额外权重（整数 ≥1）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Boss.FirstSkillSeconds</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>开战后 Boss 第一次释放技能前的等待（秒），给玩家看清阵型的时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Boss.SkillGapSeconds</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>两次技能之间的公共间隔（秒）：防止不同技能首尾相接、毫无喘息</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Boss.RecoverSeconds</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>技能最后一段命中后的收招硬直（秒），之后才回到普通攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Boss.EnrageHpRatio</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Boss 生命比例低于该值时触发一次狂暴（仅限已解锁狂暴的章节）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Boss.EnrageCooldownScale</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>狂暴后所有技能冷却乘以该系数（越小越频繁）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Boss.CooldownPerChapter</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>每高一章，技能冷却缩短的比例：冷却 × (1 − (章节−1) × 该值)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Boss.PowerPerChapter</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>每高一章，技能伤害提高的比例：倍率 × (1 + (章节−1) × 该值)</t>
         </is>
       </c>
     </row>

--- a/RevGame_Client/配置表/战斗数值参数.xlsx
+++ b/RevGame_Client/配置表/战斗数值参数.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRule" sheetId="1" r:id="R0c6e8023c6414ec9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="2" r:id="R51fe0f7b24634135"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRule" sheetId="1" r:id="R6a8f75bacb914147"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="2" r:id="R80f8524bcc9a433c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -74,7 +74,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -93,6 +93,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -541,10 +544,10 @@
         <x:v>Battle.EnemyMoveEveryTicks</x:v>
       </x:c>
       <x:c r="B9" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
-        <x:v>敌人每隔几个行动周期最多移动一次（整数≥1）；默认2个周期=2.5秒，不改变攻击频率。</x:v>
+        <x:v>敌人移动冷却为本值×标准行动周期（整数≥1）；当前1即1.25秒；不改变攻击频率。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
@@ -1361,30 +1364,60 @@
         <x:v>本轮额外攻击/攻速/生命加成上限；防御为等效耐久倍率加成</x:v>
       </x:c>
     </x:row>
-    <x:row r="84">
-      <x:c r="A84" t="str"/>
-      <x:c r="B84" t="str"/>
-      <x:c r="C84" t="str"/>
-    </x:row>
-    <x:row r="85">
-      <x:c r="A85" t="str"/>
-      <x:c r="B85" t="str"/>
-      <x:c r="C85" t="str"/>
-    </x:row>
-    <x:row r="86">
-      <x:c r="A86" t="str"/>
-      <x:c r="B86" t="str"/>
-      <x:c r="C86" t="str"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="A87" t="str"/>
-      <x:c r="B87" t="str"/>
-      <x:c r="C87" t="str"/>
-    </x:row>
-    <x:row r="88">
-      <x:c r="A88" t="str"/>
-      <x:c r="B88" t="str"/>
-      <x:c r="C88" t="str"/>
+    <x:row r="84" ht="44" customHeight="1">
+      <x:c r="A84" s="7" t="str">
+        <x:v>EnemyAI.AttackRate</x:v>
+      </x:c>
+      <x:c r="B84" s="7" t="n">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="C84" s="7" t="str">
+        <x:v>敌方普攻独立倍率（0.1～5）；含主将普攻，不加快技能预警；1恢复原频率，1.45提高45%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="44" customHeight="1">
+      <x:c r="A85" s="7" t="str">
+        <x:v>EnemyAI.ChaseSteps</x:v>
+      </x:c>
+      <x:c r="B85" s="7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C85" s="7" t="str">
+        <x:v>无眼近战每次冲锋最多经过的空格数（1～4）；不穿棋、不占敌眼，马步保留原走法。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="44" customHeight="1">
+      <x:c r="A86" s="7" t="str">
+        <x:v>PlayerAI.FormationEnabled</x:v>
+      </x:c>
+      <x:c r="B86" s="7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C86" s="7" t="str">
+        <x:v>远程自动整队开关（0关/1开）；只在战斗中整理散阵，不拆眼、不搬动零气棋。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="44" customHeight="1">
+      <x:c r="A87" s="7" t="str">
+        <x:v>PlayerAI.FormationMinCount</x:v>
+      </x:c>
+      <x:c r="B87" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C87" s="7" t="str">
+        <x:v>参与自动整队的远程棋最少数量（2～20）；已有相连阵型保持原位。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="44" customHeight="1">
+      <x:c r="A88" s="7" t="str">
+        <x:v>PlayerAI.FormationSeconds</x:v>
+      </x:c>
+      <x:c r="B88" s="7" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C88" s="7" t="str">
+        <x:v>自动整队检查间隔（秒，1～60）；尊重手动移动冷却，失败也消耗间隔，避免反复搜索。</x:v>
+      </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" t="str"/>

--- a/RevGame_Client/配置表/战斗数值参数.xlsx
+++ b/RevGame_Client/配置表/战斗数值参数.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRule" sheetId="1" r:id="R6a8f75bacb914147"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="2" r:id="R80f8524bcc9a433c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRule" sheetId="1" r:id="R07f92adf2063414b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="2" r:id="R7f71caaede174dc7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -775,7 +775,7 @@
         <x:v>Enemy.CountBase</x:v>
       </x:c>
       <x:c r="B30" s="4" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C30" s="4" t="str">
         <x:v>敌方每回合基础人数（整数）。</x:v>
@@ -797,7 +797,7 @@
         <x:v>Enemy.CountMax</x:v>
       </x:c>
       <x:c r="B32" s="4" t="n">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C32" s="4" t="str">
         <x:v>敌方每回合人数上限（整数）。</x:v>
@@ -852,7 +852,7 @@
         <x:v>Deploy.StartSeconds</x:v>
       </x:c>
       <x:c r="B37" s="4" t="n">
-        <x:v>2.5</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="C37" s="4" t="str">
         <x:v>战斗中敌方第一次补兵的最早时刻（秒），预留开局观察时间。</x:v>
@@ -888,7 +888,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C40" s="4" t="str">
-        <x:v>本回合补兵次数预算 = 本值 + 敌方 AI 档位（整数）。</x:v>
+        <x:v>本回合增援棋子预算=本值+AI档位；按成功落地棋数计数，不按窗口计数。</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="28" customHeight="1">
@@ -896,7 +896,7 @@
         <x:v>Deploy.IntervalMinSeconds</x:v>
       </x:c>
       <x:c r="B41" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C41" s="4" t="str">
         <x:v>补兵间隔的下限（秒）。</x:v>
@@ -907,7 +907,7 @@
         <x:v>Deploy.IntervalBaseSeconds</x:v>
       </x:c>
       <x:c r="B42" s="4" t="n">
-        <x:v>4.5</x:v>
+        <x:v>2.25</x:v>
       </x:c>
       <x:c r="C42" s="4" t="str">
         <x:v>补兵间隔 = max(下限, 本值 − AI档位 × 每档缩短秒数)。</x:v>
@@ -918,7 +918,7 @@
         <x:v>Deploy.IntervalPerLevelSeconds</x:v>
       </x:c>
       <x:c r="B43" s="4" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="C43" s="4" t="str">
         <x:v>AI 档位每提升一档缩短的补兵间隔（秒）。</x:v>
@@ -1083,7 +1083,7 @@
         <x:v>Round.NormalPerChapter</x:v>
       </x:c>
       <x:c r="B58" s="4" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C58" s="4" t="str">
         <x:v>每章普通回合数（整数）；第 N+1 回合是 Boss 回合；选关/跳过回合等界面与此联动。</x:v>
@@ -1419,20 +1419,93 @@
         <x:v>自动整队检查间隔（秒，1～60）；尊重手动移动冷却，失败也消耗间隔，避免反复搜索。</x:v>
       </x:c>
     </x:row>
-    <x:row r="89">
-      <x:c r="A89" t="str"/>
-      <x:c r="B89" t="str"/>
-      <x:c r="C89" t="str"/>
-    </x:row>
-    <x:row r="90">
-      <x:c r="A90" t="str"/>
-      <x:c r="B90" t="str"/>
-      <x:c r="C90" t="str"/>
-    </x:row>
-    <x:row r="91">
-      <x:c r="A91" t="str"/>
-      <x:c r="B91" t="str"/>
-      <x:c r="C91" t="str"/>
+    <x:row r="89" ht="48" customHeight="1">
+      <x:c r="A89" s="7" t="str">
+        <x:v>Deploy.BatchCount</x:v>
+      </x:c>
+      <x:c r="B89" s="7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C89" s="7" t="str">
+        <x:v>每个增援窗口最多落子数量（1～2）；每颗落地后重新检查人数、空格和气眼，不能穿透总预算。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="48" customHeight="1">
+      <x:c r="A90" s="7" t="str">
+        <x:v>Damage.CriticalChance</x:v>
+      </x:c>
+      <x:c r="B90" s="7" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="C90" s="7" t="str">
+        <x:v>玩家普通攻击暴击概率（0～1）；每次真实出手独立抽取，环境/Boss技能不抽取。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="48" customHeight="1">
+      <x:c r="A91" s="7" t="str">
+        <x:v>Damage.CriticalMultiplier</x:v>
+      </x:c>
+      <x:c r="B91" s="7" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="C91" s="7" t="str">
+        <x:v>暴击伤害倍率（1～10）；先乘真实伤害再结算护盾、防御，仅实际扣血才给暴击积分。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="48" customHeight="1">
+      <x:c r="A92" s="7" t="str">
+        <x:v>Score.KillPoints</x:v>
+      </x:c>
+      <x:c r="B92" s="7" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C92" s="7" t="str">
+        <x:v>玩家普通攻击或友方支援击杀一颗敌棋的基础积分（整数0～100000）；环境波动不归玩家击杀。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="48" customHeight="1">
+      <x:c r="A93" s="7" t="str">
+        <x:v>Score.CriticalPoints</x:v>
+      </x:c>
+      <x:c r="B93" s="7" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C93" s="7" t="str">
+        <x:v>一次造成真实扣血的玩家暴击基础积分（整数0～100000）；致死暴击同时获得击杀分。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="48" customHeight="1">
+      <x:c r="A94" s="7" t="str">
+        <x:v>Score.RoundGrowth</x:v>
+      </x:c>
+      <x:c r="B94" s="7" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="C94" s="7" t="str">
+        <x:v>倍率的连续回合增长系数（0～10）；进度=(章节-1)×每章回合数+回合-1。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="48" customHeight="1">
+      <x:c r="A95" s="7" t="str">
+        <x:v>Score.PieceGrowth</x:v>
+      </x:c>
+      <x:c r="B95" s="7" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="C95" s="7" t="str">
+        <x:v>倍率的存活玩家棋数增长系数（0～10）；第一颗为基准，死亡后按当前数量重新计算。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="48" customHeight="1">
+      <x:c r="A96" s="7" t="str">
+        <x:v>Score.MultiplierCap</x:v>
+      </x:c>
+      <x:c r="B96" s="7" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C96" s="7" t="str">
+        <x:v>积分倍率上限（1～1000）；倍率=min(上限,(1+进度×回合系数)×(1+额外存活棋数×棋数系数))。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RevGame_Client/配置表/战斗数值参数.xlsx
+++ b/RevGame_Client/配置表/战斗数值参数.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRule" sheetId="1" r:id="R2d5923b9dec344fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="2" r:id="Rdd6fdf97c6b74b22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRule" sheetId="1" r:id="R4258498159684b42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="2" r:id="R041a9b12de0349d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -149,24 +149,12 @@
     <x:t xml:space="preserve">Boss 加速每档增加的伤害比例；高频小额伤害取整后至少再加 1 点，保证压力可见。</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Boss.HpGrowthPerChapter</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss 大棋生命随章节递增：第 N 章 = 基础 × (1 + (N-1) × 本值)。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Enemy.HpBase</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">敌方生命基础系数（给远程对射、守眼回血和事件留出展开时间）。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Enemy.HpMultiplier</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">敌方生命额外倍率，抵消我方六牌保留、双牌升级和每轮增益带来的火力。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Enemy.HpGrowthPerRound</x:t>
   </x:si>
   <x:si>
@@ -516,9 +504,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">EnemyAI.AttackRate</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌方普攻独立倍率（0.1～5）；含主将普攻，不加快技能预警；1恢复原频率，1.45提高45%。</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">EnemyAI.ChaseSteps</x:t>
@@ -2070,916 +2055,916 @@
       </x:c>
     </x:row>
     <x:row r="23" ht="28" customHeight="1">
-      <x:c r="A23" s="6" t="s">
-        <x:v>46</x:v>
+      <x:c r="A23" s="6" t="str">
+        <x:v>Boss.HpGrowthPerChapter</x:v>
       </x:c>
       <x:c r="B23" s="6" t="n">
-        <x:v>0.16</x:v>
-      </x:c>
-      <x:c r="C23" s="6" t="s">
-        <x:v>47</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str">
+        <x:v>主将生命已随关卡基础成长；不再额外叠加章节倍率，避免后章厚血重复放大。</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="28" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B24" s="6" t="n">
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="C24" s="6" t="s">
-        <x:v>49</x:v>
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str">
+        <x:v>敌军生命基础倍率，与额外倍率组合；增加单棋承伤时间，不提高单发攻击。</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="28" customHeight="1">
       <x:c r="A25" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B25" s="6" t="n">
-        <x:v>1.2</x:v>
-      </x:c>
-      <x:c r="C25" s="6" t="s">
-        <x:v>51</x:v>
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str">
+        <x:v>敌军额外生命倍率；主将另乘Boss独立耐久。</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="28" customHeight="1">
       <x:c r="A26" s="6" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B26" s="6" t="n">
         <x:v>0.004</x:v>
       </x:c>
       <x:c r="C26" s="6" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="28" customHeight="1">
       <x:c r="A27" s="6" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B27" s="6" t="n">
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="C27" s="6" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="28" customHeight="1">
       <x:c r="A28" s="6" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B28" s="6">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C28" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="28" customHeight="1">
       <x:c r="A29" s="6" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B29" s="6">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C29" s="6" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="28" customHeight="1">
       <x:c r="A30" s="6" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B30" s="6" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C30" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="28" customHeight="1">
       <x:c r="A31" s="6" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B31" s="6">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C31" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="28" customHeight="1">
       <x:c r="A32" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B32" s="6" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C32" s="6" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="6" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B33" s="6">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C33" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="28" customHeight="1">
       <x:c r="A34" s="6" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B34" s="6" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C34" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="28" customHeight="1">
       <x:c r="A35" s="6" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B35" s="6" t="n">
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="C35" s="6" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="28" customHeight="1">
       <x:c r="A36" s="6" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B36" s="6">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C36" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
       <x:c r="A37" s="6" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B37" s="6" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C37" s="6" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="28" customHeight="1">
       <x:c r="A38" s="6" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B38" s="6" t="n">
         <x:v>28</x:v>
       </x:c>
       <x:c r="C38" s="6" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="28" customHeight="1">
       <x:c r="A39" s="6" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B39" s="6" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C39" s="6" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="28" customHeight="1">
       <x:c r="A40" s="6" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B40" s="6" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C40" s="6" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="28" customHeight="1">
       <x:c r="A41" s="6" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B41" s="6">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C41" s="6" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="28" customHeight="1">
       <x:c r="A42" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B42" s="6" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="6" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="28" customHeight="1">
       <x:c r="A43" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B43" s="6" t="n">
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="C43" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="28" customHeight="1">
       <x:c r="A44" s="6" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B44" s="6">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C44" s="6" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="28" customHeight="1">
       <x:c r="A45" s="6" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B45" s="6">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C45" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="28" customHeight="1">
       <x:c r="A46" s="6" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B46" s="6">
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="C46" s="6" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="28" customHeight="1">
       <x:c r="A47" s="6" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B47" s="6" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C47" s="6" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="28" customHeight="1">
       <x:c r="A48" s="6" t="s">
-        <x:v>96</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B48" s="6" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C48" s="6" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="28" customHeight="1">
       <x:c r="A49" s="6" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B49" s="6" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C49" s="6" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="28" customHeight="1">
       <x:c r="A50" s="6" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B50" s="6">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C50" s="6" t="s">
-        <x:v>101</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="28" customHeight="1">
       <x:c r="A51" s="6" t="s">
-        <x:v>102</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B51" s="6">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C51" s="6" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="28" customHeight="1">
       <x:c r="A52" s="6" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B52" s="6">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C52" s="6" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="28" customHeight="1">
       <x:c r="A53" s="6" t="s">
-        <x:v>106</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B53" s="6">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C53" s="6" t="s">
-        <x:v>107</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="28" customHeight="1">
       <x:c r="A54" s="6" t="s">
-        <x:v>108</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B54" s="6">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C54" s="6" t="s">
-        <x:v>109</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="28" customHeight="1">
       <x:c r="A55" s="6" t="s">
-        <x:v>110</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B55" s="6" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C55" s="6" t="s">
-        <x:v>111</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="28" customHeight="1">
       <x:c r="A56" s="6" t="s">
-        <x:v>112</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B56" s="6" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C56" s="6" t="s">
-        <x:v>113</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="28" customHeight="1">
       <x:c r="A57" s="6" t="s">
-        <x:v>114</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B57" s="6">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C57" s="6" t="s">
-        <x:v>115</x:v>
+        <x:v>111</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="28" customHeight="1">
       <x:c r="A58" s="6" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B58" s="6">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C58" s="6" t="s">
-        <x:v>117</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="28" customHeight="1">
       <x:c r="A59" s="6" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B59" s="6">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C59" s="6" t="s">
-        <x:v>119</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="28" customHeight="1">
       <x:c r="A60" s="6" t="s">
-        <x:v>120</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B60" s="6">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C60" s="6" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="28" customHeight="1">
       <x:c r="A61" s="6" t="s">
-        <x:v>122</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B61" s="6">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C61" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="28" customHeight="1">
       <x:c r="A62" s="6" t="s">
-        <x:v>124</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B62" s="6" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C62" s="6" t="s">
-        <x:v>125</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="28" customHeight="1">
       <x:c r="A63" s="6" t="s">
-        <x:v>126</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B63" s="6">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C63" s="6" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="28" customHeight="1">
       <x:c r="A64" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B64" s="6" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C64" s="6" t="s">
-        <x:v>129</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="28" customHeight="1">
       <x:c r="A65" s="6" t="s">
-        <x:v>130</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B65" s="6" t="n">
         <x:v>3.2</x:v>
       </x:c>
       <x:c r="C65" s="6" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="28" customHeight="1">
       <x:c r="A66" s="6" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B66" s="6">
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="C66" s="6" t="s">
-        <x:v>133</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="28" customHeight="1">
       <x:c r="A67" s="6" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B67" s="6">
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="C67" s="6" t="s">
-        <x:v>135</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="28" customHeight="1">
       <x:c r="A68" s="6" t="s">
-        <x:v>136</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B68" s="6">
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="C68" s="6" t="s">
-        <x:v>137</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="28" customHeight="1">
       <x:c r="A69" s="6" t="s">
-        <x:v>138</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B69" s="6">
         <x:v>0.06</x:v>
       </x:c>
       <x:c r="C69" s="6" t="s">
-        <x:v>139</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="28" customHeight="1">
       <x:c r="A70" s="6" t="s">
-        <x:v>140</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B70" s="6" t="n">
         <x:v>0.07</x:v>
       </x:c>
       <x:c r="C70" s="6" t="s">
-        <x:v>141</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="28" customHeight="1">
       <x:c r="A71" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B71" s="6">
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="C71" s="6" t="s">
-        <x:v>143</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="16.5">
       <x:c r="A72" s="6" t="s">
-        <x:v>144</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B72" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C72" s="6" t="s">
-        <x:v>145</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="16.5">
       <x:c r="A73" s="6" t="s">
-        <x:v>146</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B73" s="6">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C73" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="16.5">
       <x:c r="A74" s="6" t="s">
-        <x:v>148</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B74" s="6">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C74" s="6" t="s">
-        <x:v>149</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="16.5">
       <x:c r="A75" s="6" t="s">
-        <x:v>150</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B75" s="6" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="C75" s="6" t="s">
-        <x:v>151</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="16.5">
       <x:c r="A76" s="6" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B76" s="6">
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="C76" s="6" t="s">
-        <x:v>153</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="16.5">
       <x:c r="A77" s="6" t="s">
-        <x:v>154</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B77" s="6">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C77" s="6" t="s">
-        <x:v>155</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="16.5">
       <x:c r="A78" s="6" t="s">
-        <x:v>156</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B78" s="6">
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="C78" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="s">
-        <x:v>158</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B79" t="n">
         <x:v>0.055</x:v>
       </x:c>
       <x:c r="C79" t="s">
-        <x:v>159</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="s">
-        <x:v>160</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B80" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C80" t="s">
-        <x:v>161</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="s">
-        <x:v>162</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B81">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C81" t="s">
-        <x:v>163</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="s">
-        <x:v>164</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B82" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C82" t="s">
-        <x:v>165</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="s">
-        <x:v>166</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B83" t="n">
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="C83" t="s">
-        <x:v>167</x:v>
+        <x:v>163</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="44" customHeight="1">
       <x:c r="A84" s="7" t="s">
-        <x:v>168</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B84" s="7" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="C84" s="7" t="s">
-        <x:v>169</x:v>
+      <x:c r="C84" s="7" t="str">
+        <x:v>敌军普攻独立频率倍率；不改变技能预警和移动冷却。</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="44" customHeight="1">
       <x:c r="A85" s="7" t="s">
-        <x:v>170</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B85" s="7">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C85" s="7" t="s">
-        <x:v>171</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="44" customHeight="1">
       <x:c r="A86" s="7" t="s">
-        <x:v>172</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B86" s="7">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C86" s="7" t="s">
-        <x:v>173</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="44" customHeight="1">
       <x:c r="A87" s="7" t="s">
-        <x:v>174</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B87" s="7">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C87" s="7" t="s">
-        <x:v>175</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="44" customHeight="1">
       <x:c r="A88" s="7" t="s">
-        <x:v>176</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B88" s="7">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C88" s="7" t="s">
-        <x:v>177</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="48" customHeight="1">
       <x:c r="A89" s="7" t="s">
-        <x:v>178</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B89" s="7">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C89" s="7" t="s">
-        <x:v>179</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="48" customHeight="1">
       <x:c r="A90" s="7" t="s">
-        <x:v>180</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B90" s="7" t="n">
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="C90" s="7" t="s">
-        <x:v>181</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="48" customHeight="1">
       <x:c r="A91" s="7" t="s">
-        <x:v>182</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B91" s="7" t="n">
         <x:v>1.35</x:v>
       </x:c>
       <x:c r="C91" s="7" t="s">
-        <x:v>183</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="48" customHeight="1">
       <x:c r="A92" s="7" t="s">
-        <x:v>184</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B92" s="7">
         <x:v>100</x:v>
       </x:c>
       <x:c r="C92" s="7" t="s">
-        <x:v>185</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="48" customHeight="1">
       <x:c r="A93" s="7" t="s">
-        <x:v>186</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B93" s="7">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C93" s="7" t="s">
-        <x:v>187</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="48" customHeight="1">
       <x:c r="A94" s="7" t="s">
-        <x:v>188</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B94" s="7">
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="C94" s="7" t="s">
-        <x:v>189</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="48" customHeight="1">
       <x:c r="A95" s="7" t="s">
-        <x:v>190</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B95" s="7">
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="C95" s="7" t="s">
-        <x:v>191</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="48" customHeight="1">
       <x:c r="A96" s="7" t="s">
-        <x:v>192</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B96" s="7">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C96" s="7" t="s">
-        <x:v>193</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="7" t="s">
-        <x:v>194</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B97" s="7" t="n">
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="C97" s="7" t="s">
-        <x:v>195</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="7" t="s">
-        <x:v>196</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B98" s="7" t="n">
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="C98" s="7" t="s">
-        <x:v>197</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="7" t="s">
-        <x:v>198</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B99" s="7" t="n">
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="C99" s="7" t="s">
-        <x:v>199</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="7" t="s">
-        <x:v>200</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B100" s="7" t="n">
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="C100" s="7" t="s">
-        <x:v>201</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="7" t="s">
-        <x:v>202</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B101" s="7" t="n">
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="C101" s="7" t="s">
-        <x:v>203</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="7" t="s">
-        <x:v>204</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B102" s="7">
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="C102" s="7" t="s">
-        <x:v>205</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="7" t="s">
-        <x:v>206</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B103" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C103" s="7" t="s">
-        <x:v>207</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="7" t="s">
-        <x:v>208</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B104" s="7" t="n">
         <x:v>0.6</x:v>
       </x:c>
       <x:c r="C104" s="7" t="s">
-        <x:v>209</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="7" t="s">
-        <x:v>210</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B105" s="7" t="n">
         <x:v>0.3</x:v>
       </x:c>
       <x:c r="C105" s="7" t="s">
-        <x:v>211</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -3141,10 +3126,10 @@
         <x:v>Helper.BaseDamage</x:v>
       </x:c>
       <x:c r="B120" s="7" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C120" s="7" t="str">
-        <x:v>帮手单发基础伤害，仍走统一扣血管线</x:v>
+        <x:v>帮手普通弹幕单发基础伤害；加密弹幕以小伤害多命中呈现。</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -3177,7 +3162,7 @@
         <x:v>0.15</x:v>
       </x:c>
       <x:c r="C123" s="7" t="str">
-        <x:v>每档单发伤害增加比例</x:v>
+        <x:v>每档弹幕单发伤害与普通攻速成长比例；受档数与最低间隔限制。</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -3262,10 +3247,10 @@
         <x:v>Helper.BeamDamage</x:v>
       </x:c>
       <x:c r="B131" s="7" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C131" s="7" t="str">
-        <x:v>每个固定模拟步激光伤害，不返还积分</x:v>
+        <x:v>帮手激光每个标准模拟步基础伤害；Boss加速不放大激光每秒伤害。</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -3332,6 +3317,182 @@
       </x:c>
       <x:c r="C137" s="7" t="str">
         <x:v>远程共鸣攻速最高增加60%，钱包消费不降档，换章重置</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>Boss.HpMultiplier</x:v>
+      </x:c>
+      <x:c r="B138" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>主将额外生命倍率；与独立攻击及百分比承伤系数共同校准约180秒实战，仅出生时应用。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>Helper.BossSpeedBonus</x:v>
+      </x:c>
+      <x:c r="B139" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>Boss回合帮手普通弹幕额外攻速比例，1=提高100%；不提高远程共鸣。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>Helper.BossDamageScale</x:v>
+      </x:c>
+      <x:c r="B140" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>Boss回合帮手单发弹幕伤害倍率；与加速分开，避免火力翻倍秒杀。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>Boss.AttackMultiplier</x:v>
+      </x:c>
+      <x:c r="B141" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>主将独立攻击倍率；普攻和技能共同使用，不影响普通敌棋与护卫。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>Boss.PercentDamageScale</x:v>
+      </x:c>
+      <x:c r="B142" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>主将承受最大生命比例伤害系数；炸弹、区域、炮火共用，保留固定伤害下限。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>Helper.StormThreshold</x:v>
+      </x:c>
+      <x:c r="B143" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>风暴触发上界：存活玩家棋数大于0且小于此数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>Helper.StormMissileSeconds</x:v>
+      </x:c>
+      <x:c r="B144" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>风暴导弹间隔，模拟秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>Helper.StormMissileDamage</x:v>
+      </x:c>
+      <x:c r="B145" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>风暴导弹每次直接命中基础伤害</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>Helper.StormBlastRadius</x:v>
+      </x:c>
+      <x:c r="B146" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>导弹爆炸半径，棋盘格；溅射为直接伤害的一半</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>Helper.StormJellySeconds</x:v>
+      </x:c>
+      <x:c r="B147" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>风暴水母弹幕间隔，模拟秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>Helper.StormJellyCount</x:v>
+      </x:c>
+      <x:c r="B148" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>每轮水母颗数，按敌棋稳定轮转</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>Helper.StormJellyDamage</x:v>
+      </x:c>
+      <x:c r="B149" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>单颗水母基础伤害</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>Helper.StormBeamSeconds</x:v>
+      </x:c>
+      <x:c r="B150" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>风暴激光持续模拟秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str">
+        <x:v>Helper.StormBeamCooldown</x:v>
+      </x:c>
+      <x:c r="B151" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>风暴激光启动间隔，模拟秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str">
+        <x:v>Helper.StormBeamDps</x:v>
+      </x:c>
+      <x:c r="B152" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>风暴激光每个命中敌人的每秒基础伤害</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>Helper.StormBeamWidth</x:v>
+      </x:c>
+      <x:c r="B153" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>风暴激光完整宽度，棋盘格，几何检测与画面共用</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3349,66 +3510,66 @@
   <x:sheetData>
     <x:row r="1" ht="40" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="44" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>214</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>215</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="44" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>216</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>217</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="44" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>218</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>219</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="44" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>220</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>221</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="66" customHeight="1">
       <x:c r="A6" s="2" t="s">
-        <x:v>222</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>223</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="40" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>224</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>225</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="66" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>226</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>227</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/RevGame_Client/配置表/战斗数值参数.xlsx
+++ b/RevGame_Client/配置表/战斗数值参数.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRule" sheetId="1" r:id="R4258498159684b42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="2" r:id="R041a9b12de0349d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRule" sheetId="1" r:id="R6590114c9fb648b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="2" r:id="R0d3502da77b646c6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2510,7 +2510,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B64" s="6" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C64" s="6" t="s">
         <x:v>125</x:v>
@@ -2521,7 +2521,7 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B65" s="6" t="n">
-        <x:v>3.2</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="C65" s="6" t="s">
         <x:v>127</x:v>
@@ -2531,8 +2531,8 @@
       <x:c r="A66" s="6" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B66" s="6">
-        <x:v>0.6</x:v>
+      <x:c r="B66" s="6" t="n">
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="C66" s="6" t="s">
         <x:v>129</x:v>
@@ -3324,10 +3324,10 @@
         <x:v>Boss.HpMultiplier</x:v>
       </x:c>
       <x:c r="B138" t="n">
-        <x:v>65</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C138" t="str">
-        <x:v>主将额外生命倍率；与独立攻击及百分比承伤系数共同校准约180秒实战，仅出生时应用。</x:v>
+        <x:v>2026-10-29三种子18场Boss实测中位283秒（原164秒）；与百分比伤害折减0.13、攻击倍率0.4配套，不保证每局固定时长</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -3357,7 +3357,7 @@
         <x:v>Boss.AttackMultiplier</x:v>
       </x:c>
       <x:c r="B141" t="n">
-        <x:v>0.35</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="C141" t="str">
         <x:v>主将独立攻击倍率；普攻和技能共同使用，不影响普通敌棋与护卫。</x:v>
@@ -3368,7 +3368,7 @@
         <x:v>Boss.PercentDamageScale</x:v>
       </x:c>
       <x:c r="B142" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.13</x:v>
       </x:c>
       <x:c r="C142" t="str">
         <x:v>主将承受最大生命比例伤害系数；炸弹、区域、炮火共用，保留固定伤害下限。</x:v>
@@ -3493,6 +3493,50 @@
       </x:c>
       <x:c r="C153" t="str">
         <x:v>风暴激光完整宽度，棋盘格，几何检测与画面共用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str">
+        <x:v>Boss.CommonSkillsPerExclusive</x:v>
+      </x:c>
+      <x:c r="B154" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>每3次通用主动技能穿插1次本章专属，组内轮换且仍检查冷却与合法目标</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str">
+        <x:v>Helper.ProtectionHealPerSecond</x:v>
+      </x:c>
+      <x:c r="B155" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>战斗只剩1枚存活玩家棋时，每秒恢复其最大生命30%；不复活、不提供无敌</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str">
+        <x:v>Helper.ProtectionAttackBonus</x:v>
+      </x:c>
+      <x:c r="B156" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>最后单棋保护攻击+50%，同伴补入即撤销，不累计写回原始属性</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="str">
+        <x:v>Helper.ProtectionSpeedBonus</x:v>
+      </x:c>
+      <x:c r="B157" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>最后单棋保护攻速+50%，与已有加成相乘，回合退出撤销</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/RevGame_Client/配置表/战斗数值参数.xlsx
+++ b/RevGame_Client/配置表/战斗数值参数.xlsx
@@ -2,635 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRule" sheetId="1" r:id="R6590114c9fb648b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="2" r:id="R0d3502da77b646c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRule" sheetId="1" r:id="Rd38310f0c7904c94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="2" r:id="Rd78e5e56a7ea4999"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Value</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Note</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">string</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">float</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">参数编号；代码按此名称读取，请勿改名。新增参数需程序同步读取，表里多出代码不认识的编号会在启动时报错</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">参数值；次数、格数、档位等必须填整数，比例用小数（0.25=25%）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">含义、单位与取值说明（给策划看，程序不读取）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Battle.DurationSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">普通回合战斗限时（秒）；Boss 回合不限时。到点按双方剩余总血量判胜负。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Battle.TickSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">标准行动周期（秒）：普通棋攒满一个周期出手一次；同时是模拟与敌人移动的时间基准。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Battle.StepsPerTick</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">一个行动周期拆成几个固定模拟小步（整数 ≥1）。越大远程分次出手越细，计算量越大。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Battle.AttackSpeedScale</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">攻击提速倍率：只乘出手进度，不改变模拟时钟，因此不会加快敌人走位、增益或回合倒计时。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Battle.CombatBaseScale</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">单发伤害基础系数。实际伤害系数 = 本值 ÷ 攻击提速倍率：提高出手频率时用它摊薄单发伤害，维持总火力。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Battle.EnemyMoveEveryTicks</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌人移动冷却为本值×标准行动周期（整数≥1）；当前1即1.25秒；不改变攻击频率。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Battle.EyeHealSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">我方眼位四邻回血间隔，秒</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Battle.EyeHealRatio</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">我方眼位四邻每秒回复各自最大生命3%；多个眼不叠加</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Battle.EyeHealMinEyes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">历史兼容字段；新规则按是否紧邻有效我方眼判定，不按整群眼数回血</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Damage.BaseMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">基础伤害倍率（公式里的单位 1，保持 1 即可）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Damage.LockedMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">目标被锁死（气为 0）时受到的伤害倍率。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Damage.IsolatedMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">目标孤立（只剩自己一格相连）时受到的伤害倍率。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Damage.LinkPerCell</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">攻击方每多一格相连棋，攻击额外加成的比例。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Damage.LinkMax</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">相连加成的上限比例。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Damage.ClassBonus</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">职业加成：同职业在场数量每达到一个门槛增加的攻击比例。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Damage.ClassThresholdLow</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">职业加成第一档门槛：同职业在场棋数（整数）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Damage.ClassThresholdHigh</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">职业加成第二档门槛：同职业在场棋数（整数）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss.AccelerationSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss 回合“决死加速”：每满多少秒加一档（秒）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss.AccelerationBonus</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss 加速每档增加的伤害比例；高频小额伤害取整后至少再加 1 点，保证压力可见。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enemy.HpBase</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enemy.HpMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enemy.HpGrowthPerRound</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌方生命随连续回合进度递增：× (1 + 进度 × 本值)；进度跨章不归零。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enemy.AttackGrowthPerRound</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌方攻击随连续回合进度递增：× (1 + 进度 × 本值)。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enemy.AiRoundsPerLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌方 AI 档位每隔多少个连续回合提升一档（整数 ≥1）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enemy.AiMaxLevel</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌方 AI 最高档位（整数，1~4）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enemy.CountBase</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌方每回合基础人数（整数）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enemy.CountRoundsPerExtra</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">每隔多少个连续回合敌方多一个人（整数 ≥1）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enemy.CountMax</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌方每回合人数上限（整数）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enemy.PressureStarDivisor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">继承阵容压力 = 存活我方棋星级总和 ÷ 本值（至少为 1）；用于按我方强度动态抬高敌方血攻。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enemy.PressureHpMax</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">继承阵容压力对敌方生命倍率的上限（压力平方后的封顶值）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enemy.PressureAttackMax</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">继承阵容压力对敌方攻击倍率的上限（压力开方后的封顶值）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Enemy.ArcherRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌方弓箭手直线射程（格，整数）；保留阻挡判定，与重弩跨盘攻击不同。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Deploy.StartSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">战斗中敌方第一次补兵的最早时刻（秒），预留开局观察时间。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Deploy.StopSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">到这个时刻起不再补兵（秒），避免与决胜支援形成无限拉锯。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Deploy.LivingCap</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌方在场棋数上限（整数）；死亡棋子不占额度。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Deploy.BaseCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">本回合增援棋子预算=本值+AI档位；按成功落地棋数计数，不按窗口计数。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Deploy.IntervalMinSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">补兵间隔的下限（秒）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Deploy.IntervalBaseSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">补兵间隔 = max(下限, 本值 − AI档位 × 每档缩短秒数)。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Deploy.IntervalPerLevelSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AI 档位每提升一档缩短的补兵间隔（秒）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Deploy.MinEmptyCells</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">棋盘空格数不超过本值（整数）就不补兵，留给玩家调阵和援军。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Event.ScheduleChance</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">关闭通关辅助时，普通回合安排战斗事件的概率（0~1）；Boss 回合与辅助开启时必定安排。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Event.RareChance</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">关闭通关辅助时，抽到稀有事件组的概率（0~1）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Event.DelaySeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">一回合里第一次事件最早的战斗时刻（秒）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Event.IntervalSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">相邻两次战斗事件之间的最短间隔（秒）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Event.MaxPerRound</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">每回合战斗事件次数上限（整数）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Event.FallbackHealRatio</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">事件没有合法目标时，改为全队回复最大生命的比例。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Event.ArtilleryRadius</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">炮火支援的范围半径（格，整数）：以最密集的敌人为中心的 (2R+1)×(2R+1)。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Event.StageDelaySeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">进入僵持/决胜支援阶段后，普通战斗事件至少推迟多少秒，避免两条大标题争抢。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Assist.SupportDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">支援伤害的固定下限（整数）：炮火与僵持支援取 max(本值, 按最大生命比例计算的伤害)。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Prep.DelaySeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">准备阶段开始后多少秒发放本轮增益（秒）；开战前必须等它发放。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Prep.BuffCountMin</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">每轮抽取增益数量的下限（整数）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Prep.BuffCountMax</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">每轮抽取增益数量的上限（整数，≤ 增益总数）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Prep.RegenIntervalSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">生生不息、慧眼共鸣的周期回复间隔（秒）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Round.NormalPerChapter</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">每章普通回合数（整数）；第 N+1 回合是 Boss 回合；选关/跳过回合等界面与此联动。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Round.SkipAttackBonus</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">跳过最后一个普通回合直接挑战 Boss 时，永久获得的攻击加成比例。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Hand.KindBaseWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">抽手牌时，已解锁棋种的基础权重（整数）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Hand.ClassBonusWeight</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">场上已有同职业棋子时，该棋种额外增加的抽取权重（整数）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Upgrade.PairsPerStar</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">成功打出多少张同类牌，场上已有同类棋升一星（整数 ≥1）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reward.OutnumberedFactor</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">判定“人数落后”：我方棋数 × 本值 &lt; 敌方棋数时，奖励获得额外权重（整数 ≥1）。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss.FirstSkillSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">开战后 Boss 第一次释放技能前的等待（秒），给玩家看清阵型的时间</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss.SkillGapSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">两次技能之间的公共间隔（秒）：防止不同技能首尾相接、毫无喘息</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss.RecoverSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">技能最后一段命中后的收招硬直（秒），之后才回到普通攻击</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss.EnrageHpRatio</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss 生命比例低于该值时触发一次狂暴（仅限已解锁狂暴的章节）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss.EnrageCooldownScale</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">狂暴后所有技能冷却乘以该系数（越小越频繁）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss.CooldownPerChapter</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">每高一章，技能冷却缩短的比例：冷却 × (1 − (章节−1) × 该值)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss.PowerPerChapter</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">每高一章，技能伤害提高的比例：倍率 × (1 + (章节−1) × 该值)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Boss.CaptureHpRatio</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">主将血量不高于此比例且零气才能擒王；直接击杀仍获胜</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Event.EffectMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">战斗增益效果倍率；数量类支援也受此倍率影响</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PlayerAI.MoveSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">玩家战术移动独立冷却秒数，不随攻速加快</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PlayerAI.RetreatDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">远程在距敌不大于此格数时寻找更安全位置</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Region.IntervalSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">区域波动每3秒一次</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Region.WarningSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">区域高亮预警秒数</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Region.Size</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">方形区域边长，单位格</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Region.CellDelaySeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">区域逐格波动间隔秒数（按行序号）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Region.DamageHpRatio</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">仅扣区域内敌棋最大生命15%；大棋每次仅受击一次</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bomb.IntervalSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">能量巨大每8秒一次</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bomb.WarningSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">炸弹落地蓄力秒数，到点统一命中</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bomb.DamageHpRatio</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">直接扣全场敌棋最大生命30%</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Combat.BuffCap</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">本轮额外攻击/攻速/生命加成上限；防御为等效耐久倍率加成</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EnemyAI.AttackRate</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EnemyAI.ChaseSteps</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">无眼近战每次冲锋最多经过的空格数（1～4）；不穿棋、不占敌眼，马步保留原走法。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PlayerAI.FormationEnabled</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">远程自动整队开关（0关/1开）；只在战斗中整理散阵，不拆眼、不搬动零气棋。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PlayerAI.FormationMinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">参与自动整队的远程棋最少数量（2～20）；已有相连阵型保持原位。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PlayerAI.FormationSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">自动整队检查间隔（秒，1～60）；尊重手动移动冷却，失败也消耗间隔，避免反复搜索。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Deploy.BatchCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">每个增援窗口最多落子数量（1～2）；每颗落地后重新检查人数、空格和气眼，不能穿透总预算。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Damage.CriticalChance</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">玩家普通攻击暴击概率（0～1）；每次真实出手独立抽取，环境/Boss技能不抽取。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Damage.CriticalMultiplier</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">暴击伤害倍率（1～10）；先乘真实伤害再结算护盾、防御，仅实际扣血才给暴击积分。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Score.KillPoints</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">玩家普通攻击或友方支援击杀一颗敌棋的基础积分（整数0～100000）；环境波动不归玩家击杀。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Score.CriticalPoints</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">一次造成真实扣血的玩家暴击基础积分（整数0～100000）；致死暴击同时获得击杀分。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Score.RoundGrowth</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">倍率的连续回合增长系数（0～10）；进度=(章节-1)×每章回合数+回合-1。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Score.PieceGrowth</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">倍率的存活玩家棋数增长系数（0～10）；第一颗为基准，死亡后按当前数量重新计算。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Score.MultiplierCap</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">积分倍率上限（1～1000）；倍率=min(上限,(1+进度×回合系数)×(1+额外存活棋数×棋数系数))。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Eye.PlayerAttackBonus</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">我方驻守己方眼位攻击加成；1表示加100%</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Eye.PlayerSpeedBonus</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">我方驻守己方眼位攻速加成；1表示加100%</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Eye.PlayerDefenseBonus</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">我方驻守己方眼位防御加成；1表示同等伤害减半</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Eye.EnemyAttackBonus</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌方驻眼不增加攻击力</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Eye.EnemySpeedBonus</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">敌方驻眼仅增加50%攻速，不增加攻击或防御</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Eye.GuardDefenseBonus</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">有效我方眼上下左右友军防御+50%；多个眼不叠加</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Eye.SupportSeconds</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">战斗每3秒向一个空的我方眼补一颗弩兵；无空眼跳过</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Eye.ReviveHpRatio</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">有效我方驻眼棋致死时原地回满生命；每颗一生仅一次</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Eye.ReviveHealRatio</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">驻眼复活时四邻存活友军各回复最大生命40%；大棋去重</x:t>
-  </x:si>
   <x:si>
     <x:t xml:space="preserve">战斗数值参数</x:t>
   </x:si>
@@ -1813,245 +1192,245 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="s">
-        <x:v>2</x:v>
+      <x:c r="A1" s="3" t="str">
+        <x:v>Id</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="str">
+        <x:v>Note</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
-      <x:c r="A2" s="4" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="s">
+      <x:c r="A2" s="4" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="str">
+        <x:v>string</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="120" customHeight="1">
+      <x:c r="A3" s="5" t="str">
+        <x:v>参数编号；代码按此名称读取，请勿改名。新增参数需程序同步读取，表里多出代码不认识的编号会在启动时报错</x:v>
+      </x:c>
+      <x:c r="B3" s="5" t="str">
+        <x:v>参数值；次数、格数、档位等必须填整数，比例用小数（0.25=25%）</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="str">
+        <x:v>含义、单位与取值说明（给策划看，程序不读取）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>Battle.DurationSeconds</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>普通回合战斗限时（秒）；Boss 回合不限时。到点按双方剩余总血量判胜负。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>Battle.TickSeconds</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>标准行动周期（秒）：普通棋攒满一个周期出手一次；同时是模拟与敌人移动的时间基准。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="28" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>Battle.StepsPerTick</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C2" s="4" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="120" customHeight="1">
-      <x:c r="A3" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B3" s="5" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="6" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B4" s="6">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="28" customHeight="1">
-      <x:c r="A5" s="6" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B5" s="6">
-        <x:v>1.25</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="28" customHeight="1">
-      <x:c r="A6" s="6" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B6" s="6">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>13</x:v>
+      <x:c r="C6" s="6" t="str">
+        <x:v>一个行动周期拆成几个固定模拟小步（整数 ≥1）。越大远程分次出手越细，计算量越大。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
-      <x:c r="A7" s="6" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B7" s="6">
+      <x:c r="A7" s="6" t="str">
+        <x:v>Battle.AttackSpeedScale</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="n">
         <x:v>1.35</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="s">
-        <x:v>15</x:v>
+      <x:c r="C7" s="6" t="str">
+        <x:v>攻击提速倍率：只乘出手进度，不改变模拟时钟，因此不会加快敌人走位、增益或回合倒计时。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
-      <x:c r="A8" s="6" t="s">
-        <x:v>16</x:v>
+      <x:c r="A8" s="6" t="str">
+        <x:v>Battle.CombatBaseScale</x:v>
       </x:c>
       <x:c r="B8" s="6" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="s">
-        <x:v>17</x:v>
+      <x:c r="C8" s="6" t="str">
+        <x:v>单发伤害基础系数。实际伤害系数 = 本值 ÷ 攻击提速倍率：提高出手频率时用它摊薄单发伤害，维持总火力。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
-      <x:c r="A9" s="6" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B9" s="6">
+      <x:c r="A9" s="6" t="str">
+        <x:v>Battle.EnemyMoveEveryTicks</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="s">
-        <x:v>19</x:v>
+      <x:c r="C9" s="6" t="str">
+        <x:v>敌人移动冷却为本值×标准行动周期（整数≥1）；当前1即1.25秒；不改变攻击频率。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
-      <x:c r="A10" s="6" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B10" s="6">
+      <x:c r="A10" s="6" t="str">
+        <x:v>Battle.EyeHealSeconds</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="s">
-        <x:v>21</x:v>
+      <x:c r="C10" s="6" t="str">
+        <x:v>我方眼位四邻回血间隔，秒</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
-      <x:c r="A11" s="6" t="s">
-        <x:v>22</x:v>
+      <x:c r="A11" s="6" t="str">
+        <x:v>Battle.EyeHealRatio</x:v>
       </x:c>
       <x:c r="B11" s="6" t="n">
         <x:v>0.018</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="s">
-        <x:v>23</x:v>
+      <x:c r="C11" s="6" t="str">
+        <x:v>我方眼位四邻每秒回复各自最大生命3%；多个眼不叠加</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
-      <x:c r="A12" s="6" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B12" s="6">
+      <x:c r="A12" s="6" t="str">
+        <x:v>Battle.EyeHealMinEyes</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="s">
-        <x:v>25</x:v>
+      <x:c r="C12" s="6" t="str">
+        <x:v>历史兼容字段；新规则按是否紧邻有效我方眼判定，不按整群眼数回血</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="28" customHeight="1">
-      <x:c r="A13" s="6" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B13" s="6">
+      <x:c r="A13" s="6" t="str">
+        <x:v>Damage.BaseMultiplier</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C13" s="6" t="s">
-        <x:v>27</x:v>
+      <x:c r="C13" s="6" t="str">
+        <x:v>基础伤害倍率（公式里的单位 1，保持 1 即可）。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="28" customHeight="1">
-      <x:c r="A14" s="6" t="s">
-        <x:v>28</x:v>
+      <x:c r="A14" s="6" t="str">
+        <x:v>Damage.LockedMultiplier</x:v>
       </x:c>
       <x:c r="B14" s="6" t="n">
         <x:v>1.6</x:v>
       </x:c>
-      <x:c r="C14" s="6" t="s">
-        <x:v>29</x:v>
+      <x:c r="C14" s="6" t="str">
+        <x:v>目标被锁死（气为 0）时受到的伤害倍率。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="28" customHeight="1">
-      <x:c r="A15" s="6" t="s">
-        <x:v>30</x:v>
+      <x:c r="A15" s="6" t="str">
+        <x:v>Damage.IsolatedMultiplier</x:v>
       </x:c>
       <x:c r="B15" s="6" t="n">
         <x:v>1.1</x:v>
       </x:c>
-      <x:c r="C15" s="6" t="s">
-        <x:v>31</x:v>
+      <x:c r="C15" s="6" t="str">
+        <x:v>目标孤立（只剩自己一格相连）时受到的伤害倍率。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="28" customHeight="1">
-      <x:c r="A16" s="6" t="s">
-        <x:v>32</x:v>
+      <x:c r="A16" s="6" t="str">
+        <x:v>Damage.LinkPerCell</x:v>
       </x:c>
       <x:c r="B16" s="6" t="n">
         <x:v>0.025</x:v>
       </x:c>
-      <x:c r="C16" s="6" t="s">
-        <x:v>33</x:v>
+      <x:c r="C16" s="6" t="str">
+        <x:v>攻击方每多一格相连棋，攻击额外加成的比例。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="28" customHeight="1">
-      <x:c r="A17" s="6" t="s">
-        <x:v>34</x:v>
+      <x:c r="A17" s="6" t="str">
+        <x:v>Damage.LinkMax</x:v>
       </x:c>
       <x:c r="B17" s="6" t="n">
         <x:v>0.15</x:v>
       </x:c>
-      <x:c r="C17" s="6" t="s">
-        <x:v>35</x:v>
+      <x:c r="C17" s="6" t="str">
+        <x:v>相连加成的上限比例。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="28" customHeight="1">
-      <x:c r="A18" s="6" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B18" s="6">
+      <x:c r="A18" s="6" t="str">
+        <x:v>Damage.ClassBonus</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="C18" s="6" t="s">
-        <x:v>37</x:v>
+      <x:c r="C18" s="6" t="str">
+        <x:v>职业加成：同职业在场数量每达到一个门槛增加的攻击比例。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="28" customHeight="1">
-      <x:c r="A19" s="6" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B19" s="6">
+      <x:c r="A19" s="6" t="str">
+        <x:v>Damage.ClassThresholdLow</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C19" s="6" t="s">
-        <x:v>39</x:v>
+      <x:c r="C19" s="6" t="str">
+        <x:v>职业加成第一档门槛：同职业在场棋数（整数）。</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="28" customHeight="1">
-      <x:c r="A20" s="6" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B20" s="6">
+      <x:c r="A20" s="6" t="str">
+        <x:v>Damage.ClassThresholdHigh</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C20" s="6" t="s">
-        <x:v>41</x:v>
+      <x:c r="C20" s="6" t="str">
+        <x:v>职业加成第二档门槛：同职业在场棋数（整数）。</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="28" customHeight="1">
-      <x:c r="A21" s="6" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B21" s="6">
+      <x:c r="A21" s="6" t="str">
+        <x:v>Boss.AccelerationSeconds</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C21" s="6" t="s">
-        <x:v>43</x:v>
+      <x:c r="C21" s="6" t="str">
+        <x:v>Boss 回合“决死加速”：每满多少秒加一档（秒）。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="28" customHeight="1">
-      <x:c r="A22" s="6" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B22" s="6">
+      <x:c r="A22" s="6" t="str">
+        <x:v>Boss.AccelerationBonus</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="C22" s="6" t="s">
-        <x:v>45</x:v>
+      <x:c r="C22" s="6" t="str">
+        <x:v>Boss 加速每档增加的伤害比例；高频小额伤害取整后至少再加 1 点，保证压力可见。</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="28" customHeight="1">
@@ -2066,8 +1445,8 @@
       </x:c>
     </x:row>
     <x:row r="24" ht="28" customHeight="1">
-      <x:c r="A24" s="6" t="s">
-        <x:v>46</x:v>
+      <x:c r="A24" s="6" t="str">
+        <x:v>Enemy.HpBase</x:v>
       </x:c>
       <x:c r="B24" s="6" t="n">
         <x:v>1.7</x:v>
@@ -2077,8 +1456,8 @@
       </x:c>
     </x:row>
     <x:row r="25" ht="28" customHeight="1">
-      <x:c r="A25" s="6" t="s">
-        <x:v>47</x:v>
+      <x:c r="A25" s="6" t="str">
+        <x:v>Enemy.HpMultiplier</x:v>
       </x:c>
       <x:c r="B25" s="6" t="n">
         <x:v>1.4</x:v>
@@ -2088,646 +1467,646 @@
       </x:c>
     </x:row>
     <x:row r="26" ht="28" customHeight="1">
-      <x:c r="A26" s="6" t="s">
-        <x:v>48</x:v>
+      <x:c r="A26" s="6" t="str">
+        <x:v>Enemy.HpGrowthPerRound</x:v>
       </x:c>
       <x:c r="B26" s="6" t="n">
         <x:v>0.004</x:v>
       </x:c>
-      <x:c r="C26" s="6" t="s">
-        <x:v>49</x:v>
+      <x:c r="C26" s="6" t="str">
+        <x:v>敌方生命随连续回合进度递增：× (1 + 进度 × 本值)；进度跨章不归零。</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="28" customHeight="1">
-      <x:c r="A27" s="6" t="s">
-        <x:v>50</x:v>
+      <x:c r="A27" s="6" t="str">
+        <x:v>Enemy.AttackGrowthPerRound</x:v>
       </x:c>
       <x:c r="B27" s="6" t="n">
         <x:v>0.002</x:v>
       </x:c>
-      <x:c r="C27" s="6" t="s">
-        <x:v>51</x:v>
+      <x:c r="C27" s="6" t="str">
+        <x:v>敌方攻击随连续回合进度递增：× (1 + 进度 × 本值)。</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="28" customHeight="1">
-      <x:c r="A28" s="6" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B28" s="6">
+      <x:c r="A28" s="6" t="str">
+        <x:v>Enemy.AiRoundsPerLevel</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C28" s="6" t="s">
-        <x:v>53</x:v>
+      <x:c r="C28" s="6" t="str">
+        <x:v>敌方 AI 档位每隔多少个连续回合提升一档（整数 ≥1）。</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="28" customHeight="1">
-      <x:c r="A29" s="6" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B29" s="6">
+      <x:c r="A29" s="6" t="str">
+        <x:v>Enemy.AiMaxLevel</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C29" s="6" t="s">
-        <x:v>55</x:v>
+      <x:c r="C29" s="6" t="str">
+        <x:v>敌方 AI 最高档位（整数，1~4）。</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="28" customHeight="1">
-      <x:c r="A30" s="6" t="s">
-        <x:v>56</x:v>
+      <x:c r="A30" s="6" t="str">
+        <x:v>Enemy.CountBase</x:v>
       </x:c>
       <x:c r="B30" s="6" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C30" s="6" t="s">
-        <x:v>57</x:v>
+      <x:c r="C30" s="6" t="str">
+        <x:v>敌方每回合基础人数（整数）。</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="28" customHeight="1">
-      <x:c r="A31" s="6" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B31" s="6">
+      <x:c r="A31" s="6" t="str">
+        <x:v>Enemy.CountRoundsPerExtra</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C31" s="6" t="s">
-        <x:v>59</x:v>
+      <x:c r="C31" s="6" t="str">
+        <x:v>每隔多少个连续回合敌方多一个人（整数 ≥1）。</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="28" customHeight="1">
-      <x:c r="A32" s="6" t="s">
-        <x:v>60</x:v>
+      <x:c r="A32" s="6" t="str">
+        <x:v>Enemy.CountMax</x:v>
       </x:c>
       <x:c r="B32" s="6" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C32" s="6" t="s">
-        <x:v>61</x:v>
+      <x:c r="C32" s="6" t="str">
+        <x:v>敌方每回合人数上限（整数）。</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
-      <x:c r="A33" s="6" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B33" s="6">
+      <x:c r="A33" s="6" t="str">
+        <x:v>Enemy.PressureStarDivisor</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C33" s="6" t="s">
-        <x:v>63</x:v>
+      <x:c r="C33" s="6" t="str">
+        <x:v>继承阵容压力 = 存活我方棋星级总和 ÷ 本值（至少为 1）；用于按我方强度动态抬高敌方血攻。</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="28" customHeight="1">
-      <x:c r="A34" s="6" t="s">
-        <x:v>64</x:v>
+      <x:c r="A34" s="6" t="str">
+        <x:v>Enemy.PressureHpMax</x:v>
       </x:c>
       <x:c r="B34" s="6" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C34" s="6" t="s">
-        <x:v>65</x:v>
+      <x:c r="C34" s="6" t="str">
+        <x:v>继承阵容压力对敌方生命倍率的上限（压力平方后的封顶值）。</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="28" customHeight="1">
-      <x:c r="A35" s="6" t="s">
-        <x:v>66</x:v>
+      <x:c r="A35" s="6" t="str">
+        <x:v>Enemy.PressureAttackMax</x:v>
       </x:c>
       <x:c r="B35" s="6" t="n">
         <x:v>1.2</x:v>
       </x:c>
-      <x:c r="C35" s="6" t="s">
-        <x:v>67</x:v>
+      <x:c r="C35" s="6" t="str">
+        <x:v>继承阵容压力对敌方攻击倍率的上限（压力开方后的封顶值）。</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="28" customHeight="1">
-      <x:c r="A36" s="6" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B36" s="6">
+      <x:c r="A36" s="6" t="str">
+        <x:v>Enemy.ArcherRange</x:v>
+      </x:c>
+      <x:c r="B36" s="6" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C36" s="6" t="s">
-        <x:v>69</x:v>
+      <x:c r="C36" s="6" t="str">
+        <x:v>敌方弓箭手直线射程（格，整数）；保留阻挡判定，与重弩跨盘攻击不同。</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="6" t="s">
-        <x:v>70</x:v>
+      <x:c r="A37" s="6" t="str">
+        <x:v>Deploy.StartSeconds</x:v>
       </x:c>
       <x:c r="B37" s="6" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C37" s="6" t="s">
-        <x:v>71</x:v>
+      <x:c r="C37" s="6" t="str">
+        <x:v>战斗中敌方第一次补兵的最早时刻（秒），预留开局观察时间。</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="28" customHeight="1">
-      <x:c r="A38" s="6" t="s">
-        <x:v>72</x:v>
+      <x:c r="A38" s="6" t="str">
+        <x:v>Deploy.StopSeconds</x:v>
       </x:c>
       <x:c r="B38" s="6" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C38" s="6" t="s">
-        <x:v>73</x:v>
+      <x:c r="C38" s="6" t="str">
+        <x:v>到这个时刻起不再补兵（秒），避免与决胜支援形成无限拉锯。</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="28" customHeight="1">
-      <x:c r="A39" s="6" t="s">
-        <x:v>74</x:v>
+      <x:c r="A39" s="6" t="str">
+        <x:v>Deploy.LivingCap</x:v>
       </x:c>
       <x:c r="B39" s="6" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C39" s="6" t="s">
-        <x:v>75</x:v>
+      <x:c r="C39" s="6" t="str">
+        <x:v>敌方在场棋数上限（整数）；死亡棋子不占额度。</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="28" customHeight="1">
-      <x:c r="A40" s="6" t="s">
-        <x:v>76</x:v>
+      <x:c r="A40" s="6" t="str">
+        <x:v>Deploy.BaseCount</x:v>
       </x:c>
       <x:c r="B40" s="6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C40" s="6" t="s">
-        <x:v>77</x:v>
+      <x:c r="C40" s="6" t="str">
+        <x:v>本回合增援棋子预算=本值+AI档位；按成功落地棋数计数，不按窗口计数。</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="28" customHeight="1">
-      <x:c r="A41" s="6" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B41" s="6">
+      <x:c r="A41" s="6" t="str">
+        <x:v>Deploy.IntervalMinSeconds</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C41" s="6" t="s">
-        <x:v>79</x:v>
+      <x:c r="C41" s="6" t="str">
+        <x:v>补兵间隔的下限（秒）。</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="28" customHeight="1">
-      <x:c r="A42" s="6" t="s">
-        <x:v>80</x:v>
+      <x:c r="A42" s="6" t="str">
+        <x:v>Deploy.IntervalBaseSeconds</x:v>
       </x:c>
       <x:c r="B42" s="6" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C42" s="6" t="s">
-        <x:v>81</x:v>
+      <x:c r="C42" s="6" t="str">
+        <x:v>补兵间隔 = max(下限, 本值 − AI档位 × 每档缩短秒数)。</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="28" customHeight="1">
-      <x:c r="A43" s="6" t="s">
-        <x:v>82</x:v>
+      <x:c r="A43" s="6" t="str">
+        <x:v>Deploy.IntervalPerLevelSeconds</x:v>
       </x:c>
       <x:c r="B43" s="6" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="C43" s="6" t="s">
-        <x:v>83</x:v>
+      <x:c r="C43" s="6" t="str">
+        <x:v>AI 档位每提升一档缩短的补兵间隔（秒）。</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="28" customHeight="1">
-      <x:c r="A44" s="6" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B44" s="6">
+      <x:c r="A44" s="6" t="str">
+        <x:v>Deploy.MinEmptyCells</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C44" s="6" t="s">
-        <x:v>85</x:v>
+      <x:c r="C44" s="6" t="str">
+        <x:v>棋盘空格数不超过本值（整数）就不补兵，留给玩家调阵和援军。</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="28" customHeight="1">
-      <x:c r="A45" s="6" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B45" s="6">
+      <x:c r="A45" s="6" t="str">
+        <x:v>Event.ScheduleChance</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C45" s="6" t="s">
-        <x:v>87</x:v>
+      <x:c r="C45" s="6" t="str">
+        <x:v>关闭通关辅助时，普通回合安排战斗事件的概率（0~1）；Boss 回合与辅助开启时必定安排。</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="28" customHeight="1">
-      <x:c r="A46" s="6" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B46" s="6">
+      <x:c r="A46" s="6" t="str">
+        <x:v>Event.RareChance</x:v>
+      </x:c>
+      <x:c r="B46" s="6" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="C46" s="6" t="s">
-        <x:v>89</x:v>
+      <x:c r="C46" s="6" t="str">
+        <x:v>关闭通关辅助时，抽到稀有事件组的概率（0~1）。</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="28" customHeight="1">
-      <x:c r="A47" s="6" t="s">
-        <x:v>90</x:v>
+      <x:c r="A47" s="6" t="str">
+        <x:v>Event.DelaySeconds</x:v>
       </x:c>
       <x:c r="B47" s="6" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C47" s="6" t="s">
-        <x:v>91</x:v>
+      <x:c r="C47" s="6" t="str">
+        <x:v>一回合里第一次事件最早的战斗时刻（秒）。</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="28" customHeight="1">
-      <x:c r="A48" s="6" t="s">
-        <x:v>92</x:v>
+      <x:c r="A48" s="6" t="str">
+        <x:v>Event.IntervalSeconds</x:v>
       </x:c>
       <x:c r="B48" s="6" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C48" s="6" t="s">
-        <x:v>93</x:v>
+      <x:c r="C48" s="6" t="str">
+        <x:v>相邻两次战斗事件之间的最短间隔（秒）。</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="28" customHeight="1">
-      <x:c r="A49" s="6" t="s">
-        <x:v>94</x:v>
+      <x:c r="A49" s="6" t="str">
+        <x:v>Event.MaxPerRound</x:v>
       </x:c>
       <x:c r="B49" s="6" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C49" s="6" t="s">
-        <x:v>95</x:v>
+      <x:c r="C49" s="6" t="str">
+        <x:v>每回合战斗事件次数上限（整数）。</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="28" customHeight="1">
-      <x:c r="A50" s="6" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="B50" s="6">
+      <x:c r="A50" s="6" t="str">
+        <x:v>Event.FallbackHealRatio</x:v>
+      </x:c>
+      <x:c r="B50" s="6" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="C50" s="6" t="s">
-        <x:v>97</x:v>
+      <x:c r="C50" s="6" t="str">
+        <x:v>事件没有合法目标时，改为全队回复最大生命的比例。</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="28" customHeight="1">
-      <x:c r="A51" s="6" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B51" s="6">
+      <x:c r="A51" s="6" t="str">
+        <x:v>Event.ArtilleryRadius</x:v>
+      </x:c>
+      <x:c r="B51" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C51" s="6" t="s">
-        <x:v>99</x:v>
+      <x:c r="C51" s="6" t="str">
+        <x:v>炮火支援的范围半径（格，整数）：以最密集的敌人为中心的 (2R+1)×(2R+1)。</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="28" customHeight="1">
-      <x:c r="A52" s="6" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B52" s="6">
+      <x:c r="A52" s="6" t="str">
+        <x:v>Event.StageDelaySeconds</x:v>
+      </x:c>
+      <x:c r="B52" s="6" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C52" s="6" t="s">
-        <x:v>101</x:v>
+      <x:c r="C52" s="6" t="str">
+        <x:v>进入僵持/决胜支援阶段后，普通战斗事件至少推迟多少秒，避免两条大标题争抢。</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="28" customHeight="1">
-      <x:c r="A53" s="6" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="B53" s="6">
+      <x:c r="A53" s="6" t="str">
+        <x:v>Assist.SupportDamage</x:v>
+      </x:c>
+      <x:c r="B53" s="6" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C53" s="6" t="s">
-        <x:v>103</x:v>
+      <x:c r="C53" s="6" t="str">
+        <x:v>支援伤害的固定下限（整数）：炮火与僵持支援取 max(本值, 按最大生命比例计算的伤害)。</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="28" customHeight="1">
-      <x:c r="A54" s="6" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="B54" s="6">
+      <x:c r="A54" s="6" t="str">
+        <x:v>Prep.DelaySeconds</x:v>
+      </x:c>
+      <x:c r="B54" s="6" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C54" s="6" t="s">
-        <x:v>105</x:v>
+      <x:c r="C54" s="6" t="str">
+        <x:v>准备阶段开始后多少秒发放本轮增益（秒）；开战前必须等它发放。</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="28" customHeight="1">
-      <x:c r="A55" s="6" t="s">
-        <x:v>106</x:v>
+      <x:c r="A55" s="6" t="str">
+        <x:v>Prep.BuffCountMin</x:v>
       </x:c>
       <x:c r="B55" s="6" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C55" s="6" t="s">
-        <x:v>107</x:v>
+      <x:c r="C55" s="6" t="str">
+        <x:v>每轮抽取增益数量的下限（整数）。</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="28" customHeight="1">
-      <x:c r="A56" s="6" t="s">
-        <x:v>108</x:v>
+      <x:c r="A56" s="6" t="str">
+        <x:v>Prep.BuffCountMax</x:v>
       </x:c>
       <x:c r="B56" s="6" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C56" s="6" t="s">
-        <x:v>109</x:v>
+      <x:c r="C56" s="6" t="str">
+        <x:v>每轮抽取增益数量的上限（整数，≤ 增益总数）。</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="28" customHeight="1">
-      <x:c r="A57" s="6" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="B57" s="6">
+      <x:c r="A57" s="6" t="str">
+        <x:v>Prep.RegenIntervalSeconds</x:v>
+      </x:c>
+      <x:c r="B57" s="6" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C57" s="6" t="s">
-        <x:v>111</x:v>
+      <x:c r="C57" s="6" t="str">
+        <x:v>生生不息、慧眼共鸣的周期回复间隔（秒）。</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="28" customHeight="1">
-      <x:c r="A58" s="6" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="B58" s="6">
+      <x:c r="A58" s="6" t="str">
+        <x:v>Round.NormalPerChapter</x:v>
+      </x:c>
+      <x:c r="B58" s="6" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C58" s="6" t="s">
-        <x:v>113</x:v>
+      <x:c r="C58" s="6" t="str">
+        <x:v>每章普通回合数（整数）；第 N+1 回合是 Boss 回合；选关/跳过回合等界面与此联动。</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="28" customHeight="1">
-      <x:c r="A59" s="6" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="B59" s="6">
+      <x:c r="A59" s="6" t="str">
+        <x:v>Round.SkipAttackBonus</x:v>
+      </x:c>
+      <x:c r="B59" s="6" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="C59" s="6" t="s">
-        <x:v>115</x:v>
+      <x:c r="C59" s="6" t="str">
+        <x:v>跳过最后一个普通回合直接挑战 Boss 时，永久获得的攻击加成比例。</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="28" customHeight="1">
-      <x:c r="A60" s="6" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="B60" s="6">
+      <x:c r="A60" s="6" t="str">
+        <x:v>Hand.KindBaseWeight</x:v>
+      </x:c>
+      <x:c r="B60" s="6" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C60" s="6" t="s">
-        <x:v>117</x:v>
+      <x:c r="C60" s="6" t="str">
+        <x:v>抽手牌时，已解锁棋种的基础权重（整数）。</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="28" customHeight="1">
-      <x:c r="A61" s="6" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="B61" s="6">
+      <x:c r="A61" s="6" t="str">
+        <x:v>Hand.ClassBonusWeight</x:v>
+      </x:c>
+      <x:c r="B61" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C61" s="6" t="s">
-        <x:v>119</x:v>
+      <x:c r="C61" s="6" t="str">
+        <x:v>场上已有同职业棋子时，该棋种额外增加的抽取权重（整数）。</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="28" customHeight="1">
-      <x:c r="A62" s="6" t="s">
-        <x:v>120</x:v>
+      <x:c r="A62" s="6" t="str">
+        <x:v>Upgrade.PairsPerStar</x:v>
       </x:c>
       <x:c r="B62" s="6" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C62" s="6" t="s">
-        <x:v>121</x:v>
+      <x:c r="C62" s="6" t="str">
+        <x:v>成功打出多少张同类牌，场上已有同类棋升一星（整数 ≥1）。</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="28" customHeight="1">
-      <x:c r="A63" s="6" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="B63" s="6">
+      <x:c r="A63" s="6" t="str">
+        <x:v>Reward.OutnumberedFactor</x:v>
+      </x:c>
+      <x:c r="B63" s="6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C63" s="6" t="s">
-        <x:v>123</x:v>
+      <x:c r="C63" s="6" t="str">
+        <x:v>判定“人数落后”：我方棋数 × 本值 &lt; 敌方棋数时，奖励获得额外权重（整数 ≥1）。</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="28" customHeight="1">
-      <x:c r="A64" s="6" t="s">
-        <x:v>124</x:v>
+      <x:c r="A64" s="6" t="str">
+        <x:v>Boss.FirstSkillSeconds</x:v>
       </x:c>
       <x:c r="B64" s="6" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C64" s="6" t="s">
-        <x:v>125</x:v>
+      <x:c r="C64" s="6" t="str">
+        <x:v>开战后 Boss 第一次释放技能前的等待（秒），给玩家看清阵型的时间</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="28" customHeight="1">
-      <x:c r="A65" s="6" t="s">
-        <x:v>126</x:v>
+      <x:c r="A65" s="6" t="str">
+        <x:v>Boss.SkillGapSeconds</x:v>
       </x:c>
       <x:c r="B65" s="6" t="n">
         <x:v>1.25</x:v>
       </x:c>
-      <x:c r="C65" s="6" t="s">
-        <x:v>127</x:v>
+      <x:c r="C65" s="6" t="str">
+        <x:v>两次技能之间的公共间隔（秒）：防止不同技能首尾相接、毫无喘息</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="28" customHeight="1">
-      <x:c r="A66" s="6" t="s">
-        <x:v>128</x:v>
+      <x:c r="A66" s="6" t="str">
+        <x:v>Boss.RecoverSeconds</x:v>
       </x:c>
       <x:c r="B66" s="6" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="C66" s="6" t="s">
-        <x:v>129</x:v>
+      <x:c r="C66" s="6" t="str">
+        <x:v>技能最后一段命中后的收招硬直（秒），之后才回到普通攻击</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="28" customHeight="1">
-      <x:c r="A67" s="6" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="B67" s="6">
+      <x:c r="A67" s="6" t="str">
+        <x:v>Boss.EnrageHpRatio</x:v>
+      </x:c>
+      <x:c r="B67" s="6" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="C67" s="6" t="s">
-        <x:v>131</x:v>
+      <x:c r="C67" s="6" t="str">
+        <x:v>Boss 生命比例低于该值时触发一次狂暴（仅限已解锁狂暴的章节）</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="28" customHeight="1">
-      <x:c r="A68" s="6" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="B68" s="6">
+      <x:c r="A68" s="6" t="str">
+        <x:v>Boss.EnrageCooldownScale</x:v>
+      </x:c>
+      <x:c r="B68" s="6" t="n">
         <x:v>0.65</x:v>
       </x:c>
-      <x:c r="C68" s="6" t="s">
-        <x:v>133</x:v>
+      <x:c r="C68" s="6" t="str">
+        <x:v>狂暴后所有技能冷却乘以该系数（越小越频繁）</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="28" customHeight="1">
-      <x:c r="A69" s="6" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="B69" s="6">
+      <x:c r="A69" s="6" t="str">
+        <x:v>Boss.CooldownPerChapter</x:v>
+      </x:c>
+      <x:c r="B69" s="6" t="n">
         <x:v>0.06</x:v>
       </x:c>
-      <x:c r="C69" s="6" t="s">
-        <x:v>135</x:v>
+      <x:c r="C69" s="6" t="str">
+        <x:v>每高一章，技能冷却缩短的比例：冷却 × (1 − (章节−1) × 该值)</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="28" customHeight="1">
-      <x:c r="A70" s="6" t="s">
-        <x:v>136</x:v>
+      <x:c r="A70" s="6" t="str">
+        <x:v>Boss.PowerPerChapter</x:v>
       </x:c>
       <x:c r="B70" s="6" t="n">
         <x:v>0.07</x:v>
       </x:c>
-      <x:c r="C70" s="6" t="s">
-        <x:v>137</x:v>
+      <x:c r="C70" s="6" t="str">
+        <x:v>每高一章，技能伤害提高的比例：倍率 × (1 + (章节−1) × 该值)</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="28" customHeight="1">
-      <x:c r="A71" s="6" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="B71" s="6">
+      <x:c r="A71" s="6" t="str">
+        <x:v>Boss.CaptureHpRatio</x:v>
+      </x:c>
+      <x:c r="B71" s="6" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="C71" s="6" t="s">
-        <x:v>139</x:v>
+      <x:c r="C71" s="6" t="str">
+        <x:v>主将血量不高于此比例且零气才能擒王；直接击杀仍获胜</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="16.5">
-      <x:c r="A72" s="6" t="s">
-        <x:v>140</x:v>
+      <x:c r="A72" s="6" t="str">
+        <x:v>Event.EffectMultiplier</x:v>
       </x:c>
       <x:c r="B72" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C72" s="6" t="s">
-        <x:v>141</x:v>
+      <x:c r="C72" s="6" t="str">
+        <x:v>战斗增益效果倍率；数量类支援也受此倍率影响</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="16.5">
-      <x:c r="A73" s="6" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="B73" s="6">
+      <x:c r="A73" s="6" t="str">
+        <x:v>PlayerAI.MoveSeconds</x:v>
+      </x:c>
+      <x:c r="B73" s="6" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C73" s="6" t="s">
-        <x:v>143</x:v>
+      <x:c r="C73" s="6" t="str">
+        <x:v>玩家战术移动独立冷却秒数，不随攻速加快</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="16.5">
-      <x:c r="A74" s="6" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="B74" s="6">
+      <x:c r="A74" s="6" t="str">
+        <x:v>PlayerAI.RetreatDistance</x:v>
+      </x:c>
+      <x:c r="B74" s="6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C74" s="6" t="s">
-        <x:v>145</x:v>
+      <x:c r="C74" s="6" t="str">
+        <x:v>远程在距敌不大于此格数时寻找更安全位置</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="16.5">
-      <x:c r="A75" s="6" t="s">
-        <x:v>146</x:v>
+      <x:c r="A75" s="6" t="str">
+        <x:v>Region.IntervalSeconds</x:v>
       </x:c>
       <x:c r="B75" s="6" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C75" s="6" t="s">
-        <x:v>147</x:v>
+      <x:c r="C75" s="6" t="str">
+        <x:v>区域波动每3秒一次</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="16.5">
-      <x:c r="A76" s="6" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="B76" s="6">
+      <x:c r="A76" s="6" t="str">
+        <x:v>Region.WarningSeconds</x:v>
+      </x:c>
+      <x:c r="B76" s="6" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="C76" s="6" t="s">
-        <x:v>149</x:v>
+      <x:c r="C76" s="6" t="str">
+        <x:v>区域高亮预警秒数</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="16.5">
-      <x:c r="A77" s="6" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="B77" s="6">
+      <x:c r="A77" s="6" t="str">
+        <x:v>Region.Size</x:v>
+      </x:c>
+      <x:c r="B77" s="6" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C77" s="6" t="s">
-        <x:v>151</x:v>
+      <x:c r="C77" s="6" t="str">
+        <x:v>方形区域边长，单位格</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="16.5">
-      <x:c r="A78" s="6" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="B78" s="6">
+      <x:c r="A78" s="6" t="str">
+        <x:v>Region.CellDelaySeconds</x:v>
+      </x:c>
+      <x:c r="B78" s="6" t="n">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="C78" s="6" t="s">
-        <x:v>153</x:v>
+      <x:c r="C78" s="6" t="str">
+        <x:v>区域逐格波动间隔秒数（按行序号）</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" t="s">
-        <x:v>154</x:v>
+      <x:c r="A79" t="str">
+        <x:v>Region.DamageHpRatio</x:v>
       </x:c>
       <x:c r="B79" t="n">
         <x:v>0.055</x:v>
       </x:c>
-      <x:c r="C79" t="s">
-        <x:v>155</x:v>
+      <x:c r="C79" t="str">
+        <x:v>仅扣区域内敌棋最大生命15%；大棋每次仅受击一次</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" t="s">
-        <x:v>156</x:v>
+      <x:c r="A80" t="str">
+        <x:v>Bomb.IntervalSeconds</x:v>
       </x:c>
       <x:c r="B80" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C80" t="s">
-        <x:v>157</x:v>
+      <x:c r="C80" t="str">
+        <x:v>能量巨大每8秒一次</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="B81">
+      <x:c r="A81" t="str">
+        <x:v>Bomb.WarningSeconds</x:v>
+      </x:c>
+      <x:c r="B81" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C81" t="s">
-        <x:v>159</x:v>
+      <x:c r="C81" t="str">
+        <x:v>炸弹落地蓄力秒数，到点统一命中</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" t="s">
-        <x:v>160</x:v>
+      <x:c r="A82" t="str">
+        <x:v>Bomb.DamageHpRatio</x:v>
       </x:c>
       <x:c r="B82" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="C82" t="s">
-        <x:v>161</x:v>
+      <x:c r="C82" t="str">
+        <x:v>直接扣全场敌棋最大生命30%</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" t="s">
-        <x:v>162</x:v>
+      <x:c r="A83" t="str">
+        <x:v>Combat.BuffCap</x:v>
       </x:c>
       <x:c r="B83" t="n">
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="C83" t="s">
-        <x:v>163</x:v>
+      <x:c r="C83" t="str">
+        <x:v>本轮额外攻击/攻速/生命加成上限；防御为等效耐久倍率加成</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="44" customHeight="1">
-      <x:c r="A84" s="7" t="s">
-        <x:v>164</x:v>
+      <x:c r="A84" s="7" t="str">
+        <x:v>EnemyAI.AttackRate</x:v>
       </x:c>
       <x:c r="B84" s="7" t="n">
         <x:v>0.45</x:v>
@@ -2737,234 +2116,234 @@
       </x:c>
     </x:row>
     <x:row r="85" ht="44" customHeight="1">
-      <x:c r="A85" s="7" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="B85" s="7">
+      <x:c r="A85" s="7" t="str">
+        <x:v>EnemyAI.ChaseSteps</x:v>
+      </x:c>
+      <x:c r="B85" s="7" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C85" s="7" t="s">
-        <x:v>166</x:v>
+      <x:c r="C85" s="7" t="str">
+        <x:v>无眼近战每次冲锋最多经过的空格数（1～4）；不穿棋、不占敌眼，马步保留原走法。</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="44" customHeight="1">
-      <x:c r="A86" s="7" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="B86" s="7">
+      <x:c r="A86" s="7" t="str">
+        <x:v>PlayerAI.FormationEnabled</x:v>
+      </x:c>
+      <x:c r="B86" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C86" s="7" t="s">
-        <x:v>168</x:v>
+      <x:c r="C86" s="7" t="str">
+        <x:v>远程自动整队开关（0关/1开）；只在战斗中整理散阵，不拆眼、不搬动零气棋。</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="44" customHeight="1">
-      <x:c r="A87" s="7" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="B87" s="7">
+      <x:c r="A87" s="7" t="str">
+        <x:v>PlayerAI.FormationMinCount</x:v>
+      </x:c>
+      <x:c r="B87" s="7" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C87" s="7" t="s">
-        <x:v>170</x:v>
+      <x:c r="C87" s="7" t="str">
+        <x:v>参与自动整队的远程棋最少数量（2～20）；已有相连阵型保持原位。</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="44" customHeight="1">
-      <x:c r="A88" s="7" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="B88" s="7">
+      <x:c r="A88" s="7" t="str">
+        <x:v>PlayerAI.FormationSeconds</x:v>
+      </x:c>
+      <x:c r="B88" s="7" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C88" s="7" t="s">
-        <x:v>172</x:v>
+      <x:c r="C88" s="7" t="str">
+        <x:v>自动整队检查间隔（秒，1～60）；尊重手动移动冷却，失败也消耗间隔，避免反复搜索。</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="48" customHeight="1">
-      <x:c r="A89" s="7" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="B89" s="7">
+      <x:c r="A89" s="7" t="str">
+        <x:v>Deploy.BatchCount</x:v>
+      </x:c>
+      <x:c r="B89" s="7" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C89" s="7" t="s">
-        <x:v>174</x:v>
+      <x:c r="C89" s="7" t="str">
+        <x:v>每个增援窗口最多落子数量（1～2）；每颗落地后重新检查人数、空格和气眼，不能穿透总预算。</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="48" customHeight="1">
-      <x:c r="A90" s="7" t="s">
-        <x:v>175</x:v>
+      <x:c r="A90" s="7" t="str">
+        <x:v>Damage.CriticalChance</x:v>
       </x:c>
       <x:c r="B90" s="7" t="n">
         <x:v>0.15</x:v>
       </x:c>
-      <x:c r="C90" s="7" t="s">
-        <x:v>176</x:v>
+      <x:c r="C90" s="7" t="str">
+        <x:v>玩家普通攻击暴击概率（0～1）；每次真实出手独立抽取，环境/Boss技能不抽取。</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="48" customHeight="1">
-      <x:c r="A91" s="7" t="s">
-        <x:v>177</x:v>
+      <x:c r="A91" s="7" t="str">
+        <x:v>Damage.CriticalMultiplier</x:v>
       </x:c>
       <x:c r="B91" s="7" t="n">
         <x:v>1.35</x:v>
       </x:c>
-      <x:c r="C91" s="7" t="s">
-        <x:v>178</x:v>
+      <x:c r="C91" s="7" t="str">
+        <x:v>暴击伤害倍率（1～10）；先乘真实伤害再结算护盾、防御，仅实际扣血才给暴击积分。</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="48" customHeight="1">
-      <x:c r="A92" s="7" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="B92" s="7">
+      <x:c r="A92" s="7" t="str">
+        <x:v>Score.KillPoints</x:v>
+      </x:c>
+      <x:c r="B92" s="7" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C92" s="7" t="s">
-        <x:v>180</x:v>
+      <x:c r="C92" s="7" t="str">
+        <x:v>玩家普通攻击或友方支援击杀一颗敌棋的基础积分（整数0～100000）；环境波动不归玩家击杀。</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="48" customHeight="1">
-      <x:c r="A93" s="7" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="B93" s="7">
+      <x:c r="A93" s="7" t="str">
+        <x:v>Score.CriticalPoints</x:v>
+      </x:c>
+      <x:c r="B93" s="7" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C93" s="7" t="s">
-        <x:v>182</x:v>
+      <x:c r="C93" s="7" t="str">
+        <x:v>一次造成真实扣血的玩家暴击基础积分（整数0～100000）；致死暴击同时获得击杀分。</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="48" customHeight="1">
-      <x:c r="A94" s="7" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="B94" s="7">
+      <x:c r="A94" s="7" t="str">
+        <x:v>Score.RoundGrowth</x:v>
+      </x:c>
+      <x:c r="B94" s="7" t="n">
         <x:v>0.12</x:v>
       </x:c>
-      <x:c r="C94" s="7" t="s">
-        <x:v>184</x:v>
+      <x:c r="C94" s="7" t="str">
+        <x:v>倍率的连续回合增长系数（0～10）；进度=(章节-1)×每章回合数+回合-1。</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="48" customHeight="1">
-      <x:c r="A95" s="7" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="B95" s="7">
+      <x:c r="A95" s="7" t="str">
+        <x:v>Score.PieceGrowth</x:v>
+      </x:c>
+      <x:c r="B95" s="7" t="n">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="C95" s="7" t="s">
-        <x:v>186</x:v>
+      <x:c r="C95" s="7" t="str">
+        <x:v>倍率的存活玩家棋数增长系数（0～10）；第一颗为基准，死亡后按当前数量重新计算。</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="48" customHeight="1">
-      <x:c r="A96" s="7" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="B96" s="7">
+      <x:c r="A96" s="7" t="str">
+        <x:v>Score.MultiplierCap</x:v>
+      </x:c>
+      <x:c r="B96" s="7" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C96" s="7" t="s">
-        <x:v>188</x:v>
+      <x:c r="C96" s="7" t="str">
+        <x:v>积分倍率上限（1～1000）；倍率=min(上限,(1+进度×回合系数)×(1+额外存活棋数×棋数系数))。</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" s="7" t="s">
-        <x:v>189</x:v>
+      <x:c r="A97" s="7" t="str">
+        <x:v>Eye.PlayerAttackBonus</x:v>
       </x:c>
       <x:c r="B97" s="7" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="C97" s="7" t="s">
-        <x:v>190</x:v>
+      <x:c r="C97" s="7" t="str">
+        <x:v>我方驻守己方眼位攻击加成；1表示加100%</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" s="7" t="s">
-        <x:v>191</x:v>
+      <x:c r="A98" s="7" t="str">
+        <x:v>Eye.PlayerSpeedBonus</x:v>
       </x:c>
       <x:c r="B98" s="7" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="C98" s="7" t="s">
-        <x:v>192</x:v>
+      <x:c r="C98" s="7" t="str">
+        <x:v>我方驻守己方眼位攻速加成；1表示加100%</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" s="7" t="s">
-        <x:v>193</x:v>
+      <x:c r="A99" s="7" t="str">
+        <x:v>Eye.PlayerDefenseBonus</x:v>
       </x:c>
       <x:c r="B99" s="7" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="C99" s="7" t="s">
-        <x:v>194</x:v>
+      <x:c r="C99" s="7" t="str">
+        <x:v>我方驻守己方眼位防御加成；1表示同等伤害减半</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" s="7" t="s">
-        <x:v>195</x:v>
+      <x:c r="A100" s="7" t="str">
+        <x:v>Eye.EnemyAttackBonus</x:v>
       </x:c>
       <x:c r="B100" s="7" t="n">
         <x:v>0.15</x:v>
       </x:c>
-      <x:c r="C100" s="7" t="s">
-        <x:v>196</x:v>
+      <x:c r="C100" s="7" t="str">
+        <x:v>敌方驻眼不增加攻击力</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" s="7" t="s">
-        <x:v>197</x:v>
+      <x:c r="A101" s="7" t="str">
+        <x:v>Eye.EnemySpeedBonus</x:v>
       </x:c>
       <x:c r="B101" s="7" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="C101" s="7" t="s">
-        <x:v>198</x:v>
+      <x:c r="C101" s="7" t="str">
+        <x:v>敌方驻眼仅增加50%攻速，不增加攻击或防御</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
-      <x:c r="A102" s="7" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="B102" s="7">
+      <x:c r="A102" s="7" t="str">
+        <x:v>Eye.GuardDefenseBonus</x:v>
+      </x:c>
+      <x:c r="B102" s="7" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="C102" s="7" t="s">
-        <x:v>200</x:v>
+      <x:c r="C102" s="7" t="str">
+        <x:v>有效我方眼上下左右友军防御+50%；多个眼不叠加</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" s="7" t="s">
-        <x:v>201</x:v>
+      <x:c r="A103" s="7" t="str">
+        <x:v>Eye.SupportSeconds</x:v>
       </x:c>
       <x:c r="B103" s="7" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C103" s="7" t="s">
-        <x:v>202</x:v>
+      <x:c r="C103" s="7" t="str">
+        <x:v>战斗每3秒向一个空的我方眼补一颗弩兵；无空眼跳过</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" s="7" t="s">
-        <x:v>203</x:v>
+      <x:c r="A104" s="7" t="str">
+        <x:v>Eye.ReviveHpRatio</x:v>
       </x:c>
       <x:c r="B104" s="7" t="n">
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="C104" s="7" t="s">
-        <x:v>204</x:v>
+      <x:c r="C104" s="7" t="str">
+        <x:v>有效我方驻眼棋致死时原地回满生命；每颗一生仅一次</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" s="7" t="s">
-        <x:v>205</x:v>
+      <x:c r="A105" s="7" t="str">
+        <x:v>Eye.ReviveHealRatio</x:v>
       </x:c>
       <x:c r="B105" s="7" t="n">
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="C105" s="7" t="s">
-        <x:v>206</x:v>
+      <x:c r="C105" s="7" t="str">
+        <x:v>驻眼复活时四邻存活友军各回复最大生命40%；大棋去重</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -3324,10 +2703,10 @@
         <x:v>Boss.HpMultiplier</x:v>
       </x:c>
       <x:c r="B138" t="n">
-        <x:v>100</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C138" t="str">
-        <x:v>2026-10-29三种子18场Boss实测中位283秒（原164秒）；与百分比伤害折减0.13、攻击倍率0.4配套，不保证每局固定时长</x:v>
+        <x:v>2026-10-29用户指定：原100乘1.25，仅出生时应用主将生命倍率</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -3357,10 +2736,10 @@
         <x:v>Boss.AttackMultiplier</x:v>
       </x:c>
       <x:c r="B141" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="C141" t="str">
-        <x:v>主将独立攻击倍率；普攻和技能共同使用，不影响普通敌棋与护卫。</x:v>
+        <x:v>用户继续强化：0.6再乘1.25；实际普攻与技能攻击倍率，显示乘十独立</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -3537,6 +2916,72 @@
       </x:c>
       <x:c r="C157" t="str">
         <x:v>最后单棋保护攻速+50%，与已有加成相乘，回合退出撤销</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="str">
+        <x:v>Helper.BossStormAttackBonus</x:v>
+      </x:c>
+      <x:c r="B158" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>Boss回合风暴武器攻击额外+100%，普通少子风暴保持原倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="str">
+        <x:v>Helper.BossStormSpeedBonus</x:v>
+      </x:c>
+      <x:c r="B159" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>Boss回合风暴导弹/水母/激光冷却速度额外+100%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="str">
+        <x:v>Helper.BossHealPerSecond</x:v>
+      </x:c>
+      <x:c r="B160" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>Boss治疗每模拟秒恢复目标最大生命70%，不复活死棋</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="str">
+        <x:v>Helper.BossHealingAttackBonus</x:v>
+      </x:c>
+      <x:c r="B161" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>Boss治疗连线的当前棋子攻击额外+100%，换人撤销</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="str">
+        <x:v>Helper.BossHealingSpeedBonus</x:v>
+      </x:c>
+      <x:c r="B162" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>Boss治疗连线的当前棋子攻速额外+100%，换人撤销</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="str">
+        <x:v>Presentation.DamageMultiplier</x:v>
+      </x:c>
+      <x:c r="B163" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>所有伤害飘字乘十，真实扣血、伤害事件、积分和伤害合并仍保留原数值</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3554,66 +2999,66 @@
   <x:sheetData>
     <x:row r="1" ht="40" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="44" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>209</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>210</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="44" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>211</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>212</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="44" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>213</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>214</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="44" customHeight="1">
       <x:c r="A5" s="2" t="s">
-        <x:v>215</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
-        <x:v>216</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="66" customHeight="1">
       <x:c r="A6" s="2" t="s">
-        <x:v>217</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
-        <x:v>218</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="40" customHeight="1">
       <x:c r="A7" s="2" t="s">
-        <x:v>219</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>220</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="66" customHeight="1">
       <x:c r="A8" s="2" t="s">
-        <x:v>221</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>222</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/RevGame_Client/配置表/战斗数值参数.xlsx
+++ b/RevGame_Client/配置表/战斗数值参数.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRule" sheetId="1" r:id="Rd38310f0c7904c94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="2" r:id="Rd78e5e56a7ea4999"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BalanceRule" sheetId="1" r:id="Rc95d2406968944b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="2" r:id="Rdeb912defca74c4c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2984,6 +2984,919 @@
         <x:v>所有伤害飘字乘十，真实扣血、伤害事件、积分和伤害合并仍保留原数值</x:v>
       </x:c>
     </x:row>
+    <x:row r="164">
+      <x:c r="A164" t="str">
+        <x:v>Enemy.RangedAttackMultiplier</x:v>
+      </x:c>
+      <x:c r="B164" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="C164" t="str">
+        <x:v>普通敌方远程普攻攻击倍率；2026-10-31在当前基础上提高50%，不作用于近战、Boss技能或我方</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" t="str">
+        <x:v>Enemy.RangedSpeedMultiplier</x:v>
+      </x:c>
+      <x:c r="B165" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="C165" t="str">
+        <x:v>普通敌方远程攻击频率倍率；2026-10-31在当前基础上提高50%，不改变移动和技能冷却</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" t="str">
+        <x:v>PieceAttack.Swordman.Range</x:v>
+      </x:c>
+      <x:c r="B166" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C166" t="str">
+        <x:v>攻击距离，格；从身体最近边缘计算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" t="str">
+        <x:v>PieceAttack.Swordman.IntervalScale</x:v>
+      </x:c>
+      <x:c r="B167" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="C167" t="str">
+        <x:v>普攻间隔相对原职业周期倍率，越大越慢</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" t="str">
+        <x:v>PieceAttack.Swordman.PrimaryScale</x:v>
+      </x:c>
+      <x:c r="B168" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="C168" t="str">
+        <x:v>中心或首个目标伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" t="str">
+        <x:v>PieceAttack.Swordman.SecondaryScale</x:v>
+      </x:c>
+      <x:c r="B169" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C169" t="str">
+        <x:v>其它目标伤害倍率；每个实体一次</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" t="str">
+        <x:v>PieceAttack.Swordman.MaxTargets</x:v>
+      </x:c>
+      <x:c r="B170" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C170" t="str">
+        <x:v>每次攻击最多命中的不同棋子数量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" t="str">
+        <x:v>PieceAttack.Swordman.Radius</x:v>
+      </x:c>
+      <x:c r="B171" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C171" t="str">
+        <x:v>范围或连锁距离，格</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" t="str">
+        <x:v>PieceAttack.Swordman.ExecuteThreshold</x:v>
+      </x:c>
+      <x:c r="B172" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C172" t="str">
+        <x:v>收割触发血量比例，0表示关闭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" t="str">
+        <x:v>PieceAttack.Swordman.ExecuteScale</x:v>
+      </x:c>
+      <x:c r="B173" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C173" t="str">
+        <x:v>血量低于收割线时的伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" t="str">
+        <x:v>PieceAttack.Swordman.HealScale</x:v>
+      </x:c>
+      <x:c r="B174" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C174" t="str">
+        <x:v>攻击力转治疗量倍率；不复活、不突破最大生命</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" t="str">
+        <x:v>PieceAttack.Shield.Range</x:v>
+      </x:c>
+      <x:c r="B175" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C175" t="str">
+        <x:v>攻击距离，格；从身体最近边缘计算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" t="str">
+        <x:v>PieceAttack.Shield.IntervalScale</x:v>
+      </x:c>
+      <x:c r="B176" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="C176" t="str">
+        <x:v>普攻间隔相对原职业周期倍率，越大越慢</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" t="str">
+        <x:v>PieceAttack.Shield.PrimaryScale</x:v>
+      </x:c>
+      <x:c r="B177" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="C177" t="str">
+        <x:v>中心或首个目标伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" t="str">
+        <x:v>PieceAttack.Shield.SecondaryScale</x:v>
+      </x:c>
+      <x:c r="B178" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="C178" t="str">
+        <x:v>其它目标伤害倍率；每个实体一次</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" t="str">
+        <x:v>PieceAttack.Shield.MaxTargets</x:v>
+      </x:c>
+      <x:c r="B179" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C179" t="str">
+        <x:v>每次攻击最多命中的不同棋子数量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" t="str">
+        <x:v>PieceAttack.Shield.Radius</x:v>
+      </x:c>
+      <x:c r="B180" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C180" t="str">
+        <x:v>范围或连锁距离，格</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" t="str">
+        <x:v>PieceAttack.Shield.ExecuteThreshold</x:v>
+      </x:c>
+      <x:c r="B181" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C181" t="str">
+        <x:v>收割触发血量比例，0表示关闭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" t="str">
+        <x:v>PieceAttack.Shield.ExecuteScale</x:v>
+      </x:c>
+      <x:c r="B182" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C182" t="str">
+        <x:v>血量低于收割线时的伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" t="str">
+        <x:v>PieceAttack.Shield.HealScale</x:v>
+      </x:c>
+      <x:c r="B183" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="C183" t="str">
+        <x:v>攻击力转治疗量倍率；不复活、不突破最大生命</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" t="str">
+        <x:v>PieceAttack.HeavySword.Range</x:v>
+      </x:c>
+      <x:c r="B184" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C184" t="str">
+        <x:v>攻击距离，格；从身体最近边缘计算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" t="str">
+        <x:v>PieceAttack.HeavySword.IntervalScale</x:v>
+      </x:c>
+      <x:c r="B185" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="C185" t="str">
+        <x:v>普攻间隔相对原职业周期倍率，越大越慢</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" t="str">
+        <x:v>PieceAttack.HeavySword.PrimaryScale</x:v>
+      </x:c>
+      <x:c r="B186" t="n">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="C186" t="str">
+        <x:v>中心或首个目标伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" t="str">
+        <x:v>PieceAttack.HeavySword.SecondaryScale</x:v>
+      </x:c>
+      <x:c r="B187" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="C187" t="str">
+        <x:v>其它目标伤害倍率；每个实体一次</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" t="str">
+        <x:v>PieceAttack.HeavySword.MaxTargets</x:v>
+      </x:c>
+      <x:c r="B188" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C188" t="str">
+        <x:v>每次攻击最多命中的不同棋子数量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" t="str">
+        <x:v>PieceAttack.HeavySword.Radius</x:v>
+      </x:c>
+      <x:c r="B189" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C189" t="str">
+        <x:v>范围或连锁距离，格</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" t="str">
+        <x:v>PieceAttack.HeavySword.ExecuteThreshold</x:v>
+      </x:c>
+      <x:c r="B190" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C190" t="str">
+        <x:v>收割触发血量比例，0表示关闭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" t="str">
+        <x:v>PieceAttack.HeavySword.ExecuteScale</x:v>
+      </x:c>
+      <x:c r="B191" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C191" t="str">
+        <x:v>血量低于收割线时的伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" t="str">
+        <x:v>PieceAttack.HeavySword.HealScale</x:v>
+      </x:c>
+      <x:c r="B192" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C192" t="str">
+        <x:v>攻击力转治疗量倍率；不复活、不突破最大生命</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" t="str">
+        <x:v>PieceAttack.Archer.Range</x:v>
+      </x:c>
+      <x:c r="B193" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C193" t="str">
+        <x:v>攻击距离，格；从身体最近边缘计算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" t="str">
+        <x:v>PieceAttack.Archer.IntervalScale</x:v>
+      </x:c>
+      <x:c r="B194" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="C194" t="str">
+        <x:v>普攻间隔相对原职业周期倍率，越大越慢</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" t="str">
+        <x:v>PieceAttack.Archer.PrimaryScale</x:v>
+      </x:c>
+      <x:c r="B195" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="C195" t="str">
+        <x:v>中心或首个目标伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" t="str">
+        <x:v>PieceAttack.Archer.SecondaryScale</x:v>
+      </x:c>
+      <x:c r="B196" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C196" t="str">
+        <x:v>其它目标伤害倍率；每个实体一次</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" t="str">
+        <x:v>PieceAttack.Archer.MaxTargets</x:v>
+      </x:c>
+      <x:c r="B197" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C197" t="str">
+        <x:v>每次攻击最多命中的不同棋子数量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" t="str">
+        <x:v>PieceAttack.Archer.Radius</x:v>
+      </x:c>
+      <x:c r="B198" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C198" t="str">
+        <x:v>范围或连锁距离，格</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" t="str">
+        <x:v>PieceAttack.Archer.ExecuteThreshold</x:v>
+      </x:c>
+      <x:c r="B199" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C199" t="str">
+        <x:v>收割触发血量比例，0表示关闭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" t="str">
+        <x:v>PieceAttack.Archer.ExecuteScale</x:v>
+      </x:c>
+      <x:c r="B200" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C200" t="str">
+        <x:v>血量低于收割线时的伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" t="str">
+        <x:v>PieceAttack.Archer.HealScale</x:v>
+      </x:c>
+      <x:c r="B201" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C201" t="str">
+        <x:v>攻击力转治疗量倍率；不复活、不突破最大生命</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" t="str">
+        <x:v>PieceAttack.Crossbow.Range</x:v>
+      </x:c>
+      <x:c r="B202" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C202" t="str">
+        <x:v>攻击距离，格；从身体最近边缘计算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" t="str">
+        <x:v>PieceAttack.Crossbow.IntervalScale</x:v>
+      </x:c>
+      <x:c r="B203" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="C203" t="str">
+        <x:v>普攻间隔相对原职业周期倍率，越大越慢</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" t="str">
+        <x:v>PieceAttack.Crossbow.PrimaryScale</x:v>
+      </x:c>
+      <x:c r="B204" t="n">
+        <x:v>1.55</x:v>
+      </x:c>
+      <x:c r="C204" t="str">
+        <x:v>中心或首个目标伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" t="str">
+        <x:v>PieceAttack.Crossbow.SecondaryScale</x:v>
+      </x:c>
+      <x:c r="B205" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="C205" t="str">
+        <x:v>其它目标伤害倍率；每个实体一次</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" t="str">
+        <x:v>PieceAttack.Crossbow.MaxTargets</x:v>
+      </x:c>
+      <x:c r="B206" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C206" t="str">
+        <x:v>每次攻击最多命中的不同棋子数量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" t="str">
+        <x:v>PieceAttack.Crossbow.Radius</x:v>
+      </x:c>
+      <x:c r="B207" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C207" t="str">
+        <x:v>范围或连锁距离，格</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" t="str">
+        <x:v>PieceAttack.Crossbow.ExecuteThreshold</x:v>
+      </x:c>
+      <x:c r="B208" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C208" t="str">
+        <x:v>收割触发血量比例，0表示关闭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" t="str">
+        <x:v>PieceAttack.Crossbow.ExecuteScale</x:v>
+      </x:c>
+      <x:c r="B209" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C209" t="str">
+        <x:v>血量低于收割线时的伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" t="str">
+        <x:v>PieceAttack.Crossbow.HealScale</x:v>
+      </x:c>
+      <x:c r="B210" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C210" t="str">
+        <x:v>攻击力转治疗量倍率；不复活、不突破最大生命</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" t="str">
+        <x:v>PieceAttack.MageWater.Range</x:v>
+      </x:c>
+      <x:c r="B211" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C211" t="str">
+        <x:v>攻击距离，格；从身体最近边缘计算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" t="str">
+        <x:v>PieceAttack.MageWater.IntervalScale</x:v>
+      </x:c>
+      <x:c r="B212" t="n">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="C212" t="str">
+        <x:v>普攻间隔相对原职业周期倍率，越大越慢</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" t="str">
+        <x:v>PieceAttack.MageWater.PrimaryScale</x:v>
+      </x:c>
+      <x:c r="B213" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="C213" t="str">
+        <x:v>中心或首个目标伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" t="str">
+        <x:v>PieceAttack.MageWater.SecondaryScale</x:v>
+      </x:c>
+      <x:c r="B214" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="C214" t="str">
+        <x:v>其它目标伤害倍率；每个实体一次</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" t="str">
+        <x:v>PieceAttack.MageWater.MaxTargets</x:v>
+      </x:c>
+      <x:c r="B215" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C215" t="str">
+        <x:v>每次攻击最多命中的不同棋子数量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" t="str">
+        <x:v>PieceAttack.MageWater.Radius</x:v>
+      </x:c>
+      <x:c r="B216" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C216" t="str">
+        <x:v>范围或连锁距离，格</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" t="str">
+        <x:v>PieceAttack.MageWater.ExecuteThreshold</x:v>
+      </x:c>
+      <x:c r="B217" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C217" t="str">
+        <x:v>收割触发血量比例，0表示关闭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" t="str">
+        <x:v>PieceAttack.MageWater.ExecuteScale</x:v>
+      </x:c>
+      <x:c r="B218" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C218" t="str">
+        <x:v>血量低于收割线时的伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" t="str">
+        <x:v>PieceAttack.MageWater.HealScale</x:v>
+      </x:c>
+      <x:c r="B219" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C219" t="str">
+        <x:v>攻击力转治疗量倍率；不复活、不突破最大生命</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" t="str">
+        <x:v>PieceAttack.MageFire.Range</x:v>
+      </x:c>
+      <x:c r="B220" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C220" t="str">
+        <x:v>攻击距离，格；从身体最近边缘计算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" t="str">
+        <x:v>PieceAttack.MageFire.IntervalScale</x:v>
+      </x:c>
+      <x:c r="B221" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="C221" t="str">
+        <x:v>普攻间隔相对原职业周期倍率，越大越慢</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" t="str">
+        <x:v>PieceAttack.MageFire.PrimaryScale</x:v>
+      </x:c>
+      <x:c r="B222" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="C222" t="str">
+        <x:v>中心或首个目标伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" t="str">
+        <x:v>PieceAttack.MageFire.SecondaryScale</x:v>
+      </x:c>
+      <x:c r="B223" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="C223" t="str">
+        <x:v>其它目标伤害倍率；每个实体一次</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" t="str">
+        <x:v>PieceAttack.MageFire.MaxTargets</x:v>
+      </x:c>
+      <x:c r="B224" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C224" t="str">
+        <x:v>每次攻击最多命中的不同棋子数量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" t="str">
+        <x:v>PieceAttack.MageFire.Radius</x:v>
+      </x:c>
+      <x:c r="B225" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C225" t="str">
+        <x:v>范围或连锁距离，格</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" t="str">
+        <x:v>PieceAttack.MageFire.ExecuteThreshold</x:v>
+      </x:c>
+      <x:c r="B226" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C226" t="str">
+        <x:v>收割触发血量比例，0表示关闭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" t="str">
+        <x:v>PieceAttack.MageFire.ExecuteScale</x:v>
+      </x:c>
+      <x:c r="B227" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C227" t="str">
+        <x:v>血量低于收割线时的伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" t="str">
+        <x:v>PieceAttack.MageFire.HealScale</x:v>
+      </x:c>
+      <x:c r="B228" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C228" t="str">
+        <x:v>攻击力转治疗量倍率；不复活、不突破最大生命</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" t="str">
+        <x:v>PieceAttack.Priest.Range</x:v>
+      </x:c>
+      <x:c r="B229" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C229" t="str">
+        <x:v>攻击距离，格；从身体最近边缘计算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" t="str">
+        <x:v>PieceAttack.Priest.IntervalScale</x:v>
+      </x:c>
+      <x:c r="B230" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="C230" t="str">
+        <x:v>普攻间隔相对原职业周期倍率，越大越慢</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" t="str">
+        <x:v>PieceAttack.Priest.PrimaryScale</x:v>
+      </x:c>
+      <x:c r="B231" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="C231" t="str">
+        <x:v>中心或首个目标伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" t="str">
+        <x:v>PieceAttack.Priest.SecondaryScale</x:v>
+      </x:c>
+      <x:c r="B232" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C232" t="str">
+        <x:v>其它目标伤害倍率；每个实体一次</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" t="str">
+        <x:v>PieceAttack.Priest.MaxTargets</x:v>
+      </x:c>
+      <x:c r="B233" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C233" t="str">
+        <x:v>每次攻击最多命中的不同棋子数量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" t="str">
+        <x:v>PieceAttack.Priest.Radius</x:v>
+      </x:c>
+      <x:c r="B234" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C234" t="str">
+        <x:v>范围或连锁距离，格</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" t="str">
+        <x:v>PieceAttack.Priest.ExecuteThreshold</x:v>
+      </x:c>
+      <x:c r="B235" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C235" t="str">
+        <x:v>收割触发血量比例，0表示关闭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" t="str">
+        <x:v>PieceAttack.Priest.ExecuteScale</x:v>
+      </x:c>
+      <x:c r="B236" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C236" t="str">
+        <x:v>血量低于收割线时的伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" t="str">
+        <x:v>PieceAttack.Priest.HealScale</x:v>
+      </x:c>
+      <x:c r="B237" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="C237" t="str">
+        <x:v>攻击力转治疗量倍率；不复活、不突破最大生命</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" t="str">
+        <x:v>PieceAttack.Assassin.Range</x:v>
+      </x:c>
+      <x:c r="B238" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C238" t="str">
+        <x:v>攻击距离，格；从身体最近边缘计算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" t="str">
+        <x:v>PieceAttack.Assassin.IntervalScale</x:v>
+      </x:c>
+      <x:c r="B239" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="C239" t="str">
+        <x:v>普攻间隔相对原职业周期倍率，越大越慢</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" t="str">
+        <x:v>PieceAttack.Assassin.PrimaryScale</x:v>
+      </x:c>
+      <x:c r="B240" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="C240" t="str">
+        <x:v>中心或首个目标伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" t="str">
+        <x:v>PieceAttack.Assassin.SecondaryScale</x:v>
+      </x:c>
+      <x:c r="B241" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C241" t="str">
+        <x:v>其它目标伤害倍率；每个实体一次</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" t="str">
+        <x:v>PieceAttack.Assassin.MaxTargets</x:v>
+      </x:c>
+      <x:c r="B242" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C242" t="str">
+        <x:v>每次攻击最多命中的不同棋子数量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" t="str">
+        <x:v>PieceAttack.Assassin.Radius</x:v>
+      </x:c>
+      <x:c r="B243" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C243" t="str">
+        <x:v>范围或连锁距离，格</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" t="str">
+        <x:v>PieceAttack.Assassin.ExecuteThreshold</x:v>
+      </x:c>
+      <x:c r="B244" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="C244" t="str">
+        <x:v>收割触发血量比例，0表示关闭</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" t="str">
+        <x:v>PieceAttack.Assassin.ExecuteScale</x:v>
+      </x:c>
+      <x:c r="B245" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="C245" t="str">
+        <x:v>血量低于收割线时的伤害倍率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" t="str">
+        <x:v>PieceAttack.Assassin.HealScale</x:v>
+      </x:c>
+      <x:c r="B246" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C246" t="str">
+        <x:v>攻击力转治疗量倍率；不复活、不突破最大生命</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
